--- a/DOC/基本設計書/画面設計書.xlsx
+++ b/DOC/基本設計書/画面設計書.xlsx
@@ -1,47 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\soruce\DOC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMap\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEB6452-3C3A-4BAC-B74E-BA23BD53D960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558FCE52-770A-4D51-8195-74A61D0E6661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AD13DF4A-C6E9-46E2-8DF5-EB91E9C0FD90}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AD13DF4A-C6E9-46E2-8DF5-EB91E9C0FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="9" r:id="rId1"/>
     <sheet name="ログイン" sheetId="6" r:id="rId2"/>
     <sheet name="パスワード再設定" sheetId="7" r:id="rId3"/>
-    <sheet name="地図閲覧" sheetId="1" r:id="rId4"/>
-    <sheet name="分析・便利機能" sheetId="10" r:id="rId5"/>
-    <sheet name="通知機能" sheetId="11" r:id="rId6"/>
+    <sheet name="新規アカウント登録" sheetId="12" r:id="rId4"/>
+    <sheet name="地図閲覧" sheetId="1" r:id="rId5"/>
+    <sheet name="分析・便利機能" sheetId="10" r:id="rId6"/>
+    <sheet name="通知機能" sheetId="11" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="72">
   <si>
     <t>地図機能</t>
     <rPh sb="0" eb="4">
@@ -521,12 +511,78 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>DB接続失敗時</t>
+    <rPh sb="2" eb="4">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>シッパイジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>画面レイアウト（登録メールアドレスの入力）</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>登録メールアドレス</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>画面レイアウト（メールアドレスに再設定用のリンク送信）</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>サイセッテイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ソウシン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>回答が間違えています。</t>
+    <rPh sb="0" eb="2">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マチガ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>入力メールアドレスは登録がありません</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -570,6 +626,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -743,7 +807,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -796,6 +860,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1519,7 +1598,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="2085521"/>
+          <a:off x="171450" y="2248807"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -1865,7 +1944,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="8889093"/>
+          <a:off x="171450" y="9596664"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -2255,7 +2334,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="15465879"/>
+          <a:off x="171450" y="16699593"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -2851,7 +2930,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="22042664"/>
+          <a:off x="171450" y="23802521"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -3497,6 +3576,220 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>293171</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>57726</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="図 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D25DC799-54C6-47AD-B47D-64E8C0EA9210}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12504964" y="1959429"/>
+          <a:ext cx="3014600" cy="6425868"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>293170</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>11545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>204134</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="47" name="グループ化 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D6D6410-753B-147B-E2D1-E69B97CAD888}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="15519563" y="1970974"/>
+          <a:ext cx="8755607" cy="6238669"/>
+          <a:chOff x="15701689" y="1945853"/>
+          <a:chExt cx="8864464" cy="6160166"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="41" name="図 40">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{969C74B4-36BD-4872-891F-F6B75CF83A68}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="15701689" y="1945853"/>
+            <a:ext cx="8864464" cy="6160166"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="43" name="図 42">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D17B3D5-6A74-FFA2-3364-E9F28D628E3C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="18852173" y="5421922"/>
+            <a:ext cx="2491154" cy="323851"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>45872</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>92383</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>360930</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>222675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="正方形/長方形 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A455EA1-51E6-FAAA-1D57-FFC682FD25F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18863959" y="5376687"/>
+          <a:ext cx="1689971" cy="370488"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>接続に失敗しました</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3599,7 +3892,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="2085521"/>
+          <a:off x="171450" y="2248807"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -3959,7 +4252,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="8662307"/>
+          <a:off x="171450" y="9351736"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -4319,7 +4612,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="15239093"/>
+          <a:off x="171450" y="16454664"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -4533,7 +4826,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="21815879"/>
+          <a:off x="171450" y="23557593"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -4959,7 +5252,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="28392664"/>
+          <a:off x="171450" y="30660521"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -5669,10 +5962,2216 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="テキスト ボックス 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E6EEA2A-FD12-4EE4-8A49-9E293DEA4BD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683532" y="9062357"/>
+          <a:ext cx="2296432" cy="712107"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600"/>
+            <a:t>RiskMap</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="16" name="グループ化 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81CE74CE-7EE2-4542-9EA1-2CA0E224CE73}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12676414" y="16454664"/>
+          <a:ext cx="247650" cy="139700"/>
+          <a:chOff x="4089400" y="3086100"/>
+          <a:chExt cx="273050" cy="120650"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="17" name="直線コネクタ 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AF8935C-FA74-E9B9-1D2D-02F6F15EC856}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3086100"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="18" name="直線コネクタ 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0617DB84-73F8-73C2-C4B2-38189738BFDD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4089400" y="3206750"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="19" name="直線コネクタ 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB8B6830-5F26-662E-D1F8-FA95847A6407}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3143250"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>23091</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>207819</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>34636</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>11545</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="フローチャート: 代替処理 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A47EAE49-1307-4851-95A9-BFD963C24D41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5044127" y="11229605"/>
+          <a:ext cx="4093688" cy="538511"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>542636</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>115454</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>57727</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>115455</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="フローチャート: 代替処理 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E21814C6-A237-4A44-BE1F-DFC60C9DD95A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6244029" y="12361883"/>
+          <a:ext cx="1556162" cy="489858"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>メールアドレス認証</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3014600" cy="6425868"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="図 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6451A9A-B05D-49FF-9D2A-22796763DFE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9062357"/>
+          <a:ext cx="3014600" cy="6425868"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="テキスト ボックス 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14A8FE43-1383-4E1F-9EA9-3D0BEF55AFC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683532" y="16165286"/>
+          <a:ext cx="2296432" cy="712107"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600"/>
+            <a:t>RiskMap</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="24" name="グループ化 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FF6F65F-53A9-4276-8F9B-CC4DD054D09D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12676414" y="23557593"/>
+          <a:ext cx="247650" cy="139700"/>
+          <a:chOff x="4089400" y="3086100"/>
+          <a:chExt cx="273050" cy="120650"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="25" name="直線コネクタ 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ADD577F-B4D7-DF79-F5E2-19952187573D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3086100"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="26" name="直線コネクタ 25">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D5F32ED-816C-FB8E-DCD0-0EAB7C2FDD78}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4089400" y="3206750"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="27" name="直線コネクタ 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38B27B78-1597-A7AC-E56C-51155006EA0A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3143250"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3014600" cy="6425869"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="図 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFB45DB-A7F1-49BB-A7FE-8C22FDC027FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="16165286"/>
+          <a:ext cx="3014600" cy="6425869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>307739</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>230014</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>503464</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>176892</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="矢印: 下 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C503EAC5-D35A-950A-A51F-6310737B4474}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18255560" y="22518514"/>
+          <a:ext cx="1556440" cy="681664"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>500197</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>64768</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>501504</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>151637</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="矢印: 下 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88C130C8-8AD2-118F-9EDA-4F205DEC7A80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="24133845" y="18871799"/>
+          <a:ext cx="1556440" cy="681664"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="69" name="テキスト ボックス 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{699AFA7C-A284-42CB-B1B3-48367E188CD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683532" y="9062357"/>
+          <a:ext cx="2296432" cy="712107"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600"/>
+            <a:t>RiskMap</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="70" name="グループ化 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58EDA8B2-BC8D-4499-861F-91E82AA64E18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="12676414" y="9351736"/>
+          <a:ext cx="247650" cy="139700"/>
+          <a:chOff x="4089400" y="3086100"/>
+          <a:chExt cx="273050" cy="120650"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="71" name="直線コネクタ 70">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F63F47DD-A234-C64C-3301-C62B490BA419}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3086100"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="72" name="直線コネクタ 71">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{052FBF47-970A-F434-095E-D25B7FA8FC4E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4089400" y="3206750"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="73" name="直線コネクタ 72">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E3DD5AD-A81E-B0BB-D52B-A01BDC2A3EC0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3143250"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>23091</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>207819</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>34636</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>11545</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="74" name="フローチャート: 代替処理 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D96022-8E25-4DA3-9E06-4FA51DB0BE8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5044127" y="11229605"/>
+          <a:ext cx="4093688" cy="538511"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>542636</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>115454</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>57727</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>115455</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="75" name="フローチャート: 代替処理 74">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B378BA84-A348-4C88-BEDD-DBCAB117827D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6244029" y="12361883"/>
+          <a:ext cx="1556162" cy="489858"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>再設定</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3014600" cy="6425868"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="図 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E97C79AC-5BD0-47B1-A4B2-DADCC4CAC144}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9062357"/>
+          <a:ext cx="3014600" cy="6425868"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="77" name="テキスト ボックス 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91CCCB0B-20CE-4C97-B291-2B7BE1BE2B7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13188496" y="16165286"/>
+          <a:ext cx="2037897" cy="712107"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600"/>
+            <a:t>RiskMap</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="78" name="グループ化 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EC3612A-8790-4570-A676-96ED01C18DF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="25603200" y="16454664"/>
+          <a:ext cx="247650" cy="139700"/>
+          <a:chOff x="4089400" y="3086100"/>
+          <a:chExt cx="273050" cy="120650"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="79" name="直線コネクタ 78">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE556213-9223-B257-3832-BC916F16AA51}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3086100"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="80" name="直線コネクタ 79">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B9BF53A-8AD7-2423-0A3B-9CB597AF3012}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4089400" y="3206750"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="81" name="直線コネクタ 80">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E3AEC28-3EFF-56DB-C52E-8F6043A99434}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3143250"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>23091</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>207819</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>34636</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>11545</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="82" name="フローチャート: 代替処理 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96BA1EA4-1D8B-45B4-8B88-E1CCF171B613}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17290555" y="18332533"/>
+          <a:ext cx="4093688" cy="538512"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>542636</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>115454</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>57727</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>115455</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="83" name="フローチャート: 代替処理 82">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3164E86B-0FF5-4261-A22B-6AB4E6AF45E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18490457" y="19464811"/>
+          <a:ext cx="1556163" cy="489858"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>メールアドレス認証</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3014600" cy="6425868"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="図 83">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{203C3768-51DF-44D5-89F8-AA60E0D37DF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12504964" y="16165286"/>
+          <a:ext cx="3014600" cy="6425868"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8A2399D-B479-48A4-B143-374313EAEA00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="688975" y="29527500"/>
+          <a:ext cx="2311400" cy="698500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600"/>
+            <a:t>RiskMap</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="3" name="グループ化 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2C8115F-1C88-4A0C-B574-05B1F7B352F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="171450" y="779236"/>
+          <a:ext cx="247650" cy="139700"/>
+          <a:chOff x="4089400" y="3086100"/>
+          <a:chExt cx="273050" cy="120650"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="4" name="直線コネクタ 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29DDAF8A-6324-5658-DEEF-1FECC04A33D6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3086100"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="5" name="直線コネクタ 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7ADB0C0-9867-96CD-8918-40502BD9F241}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4089400" y="3206750"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="6" name="直線コネクタ 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BC4D77D-A397-C9BF-A737-E9AEE94F87E4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4095750" y="3143250"/>
+            <a:ext cx="266700" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="38100"/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="dk1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="dk1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="dk1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>23091</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>207819</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>34636</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>11545</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="フローチャート: 代替処理 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E40C036-55B2-4BED-82C1-0783666C0003}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080866" y="31640319"/>
+          <a:ext cx="4126345" cy="518101"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>11545</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>34637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>23090</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="フローチャート: 代替処理 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A2354C3-81EA-4AF7-A3DC-D59768D800C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5069320" y="32895887"/>
+          <a:ext cx="4126345" cy="510886"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>611909</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>57728</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>646545</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>57727</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="グラフィックス 8" descr="目 単色塗りつぶし">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B65A1B04-0921-4EB3-8A07-8B317CE6DCFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8412884" y="31490228"/>
+          <a:ext cx="720436" cy="714374"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>646546</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>184727</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>23091</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>184727</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="グラフィックス 9" descr="目 単色塗りつぶし">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29847070-3F90-4F8E-AB21-49C3D2146F0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8447521" y="32807852"/>
+          <a:ext cx="748145" cy="714375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>392546</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>565728</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="フローチャート: 代替処理 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1DBDCDD-A8DC-41AC-A47C-E1ECBA113ADC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6136121" y="34893251"/>
+          <a:ext cx="1544782" cy="476250"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>新規登録</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>658090</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>34637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>11544</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="フローチャート: 代替処理 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37E6F3FA-8F1F-438E-BEBC-DAEDD8613C17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5030065" y="33848387"/>
+          <a:ext cx="4154054" cy="510886"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>291811</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BC01669-6844-4EC1-B3B5-2322332370B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="29527500"/>
+          <a:ext cx="3035011" cy="6248975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5771,7 +8270,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="2085521"/>
+          <a:off x="171450" y="2248807"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -5958,8 +8457,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6694373" y="4545480"/>
-          <a:ext cx="505530" cy="503376"/>
+          <a:off x="6875801" y="4908337"/>
+          <a:ext cx="505530" cy="539662"/>
           <a:chOff x="5672930" y="4854816"/>
           <a:chExt cx="505530" cy="507004"/>
         </a:xfrm>
@@ -6157,7 +8656,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="8662307"/>
+          <a:off x="171450" y="9351736"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -6340,8 +8839,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6694373" y="11122266"/>
-          <a:ext cx="505530" cy="503375"/>
+          <a:off x="6875801" y="12011266"/>
+          <a:ext cx="505530" cy="539661"/>
           <a:chOff x="5672930" y="4854816"/>
           <a:chExt cx="505530" cy="507004"/>
         </a:xfrm>
@@ -6539,7 +9038,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="15465879"/>
+          <a:off x="171450" y="16699593"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -6726,8 +9225,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6694373" y="17925837"/>
-          <a:ext cx="505530" cy="503376"/>
+          <a:off x="6875801" y="19359123"/>
+          <a:ext cx="505530" cy="539661"/>
           <a:chOff x="5672930" y="4854816"/>
           <a:chExt cx="505530" cy="507004"/>
         </a:xfrm>
@@ -6995,7 +9494,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="22269450"/>
+          <a:off x="171450" y="24047450"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -7178,8 +9677,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6694373" y="24729409"/>
-          <a:ext cx="505530" cy="503375"/>
+          <a:off x="6875801" y="26706980"/>
+          <a:ext cx="505530" cy="539661"/>
           <a:chOff x="5672930" y="4854816"/>
           <a:chExt cx="505530" cy="507004"/>
         </a:xfrm>
@@ -7377,7 +9876,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="29073021"/>
+          <a:off x="171450" y="31395307"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -7559,8 +10058,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6694373" y="31532980"/>
-          <a:ext cx="505530" cy="503376"/>
+          <a:off x="6875801" y="34054837"/>
+          <a:ext cx="505530" cy="539662"/>
           <a:chOff x="5672930" y="4854816"/>
           <a:chExt cx="505530" cy="507004"/>
         </a:xfrm>
@@ -7828,7 +10327,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="35876593"/>
+          <a:off x="171450" y="38743164"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -8011,8 +10510,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6694373" y="38336552"/>
-          <a:ext cx="505530" cy="503375"/>
+          <a:off x="6875801" y="41402695"/>
+          <a:ext cx="505530" cy="539661"/>
           <a:chOff x="5672930" y="4854816"/>
           <a:chExt cx="505530" cy="507004"/>
         </a:xfrm>
@@ -8659,7 +11158,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -8758,7 +11257,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="2085521"/>
+          <a:off x="171450" y="2248807"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -8972,7 +11471,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="8662307"/>
+          <a:off x="171450" y="9351736"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -9155,8 +11654,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6694373" y="11122266"/>
-          <a:ext cx="505530" cy="503375"/>
+          <a:off x="6875801" y="12011266"/>
+          <a:ext cx="505530" cy="539661"/>
           <a:chOff x="5672930" y="4854816"/>
           <a:chExt cx="505530" cy="507004"/>
         </a:xfrm>
@@ -9361,7 +11860,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -9460,7 +11959,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="2085521"/>
+          <a:off x="171450" y="2248807"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -9674,7 +12173,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="8662307"/>
+          <a:off x="171450" y="9351736"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -9817,8 +12316,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6694373" y="11122266"/>
-          <a:ext cx="505530" cy="503375"/>
+          <a:off x="6875801" y="12011266"/>
+          <a:ext cx="505530" cy="539661"/>
           <a:chOff x="5672930" y="4854816"/>
           <a:chExt cx="505530" cy="507004"/>
         </a:xfrm>
@@ -10340,7 +12839,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6DDB63-8C00-4A40-8C1A-3A7C6FAD4D39}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10350,13 +12849,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66C1F85-391E-4E3A-B440-46970D05EB98}">
-  <dimension ref="A1:Q122"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:T122"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -10382,7 +12884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>16</v>
@@ -10394,25 +12896,29 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="14"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S8" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="T8" s="19"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -10431,17 +12937,17 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="D10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="D11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="D12" s="7"/>
       <c r="J12" t="s">
@@ -10449,27 +12955,27 @@
       </c>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A13" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
       <c r="D14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="D15" s="7"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
       <c r="D16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>15</v>
       </c>
@@ -10479,27 +12985,27 @@
       </c>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="D19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
       <c r="D22" s="7"/>
       <c r="H22" t="s">
@@ -10507,41 +13013,41 @@
       </c>
       <c r="Q22" s="7"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
       <c r="D23" s="7"/>
       <c r="Q23" s="7"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="6"/>
       <c r="D24" s="7"/>
       <c r="Q24" s="7"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D25" s="7"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="6"/>
       <c r="D26" s="7"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="6"/>
       <c r="D27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="6"/>
       <c r="D28" s="7"/>
       <c r="Q28" s="7"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="6"/>
       <c r="D29" s="7"/>
       <c r="Q29" s="7"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="6"/>
       <c r="D30" s="7"/>
       <c r="I30" t="s">
@@ -10549,22 +13055,22 @@
       </c>
       <c r="Q30" s="7"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="6"/>
       <c r="D31" s="7"/>
       <c r="Q31" s="7"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="6"/>
       <c r="D32" s="7"/>
       <c r="Q32" s="7"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A33" s="6"/>
       <c r="D33" s="7"/>
       <c r="Q33" s="7"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -10583,14 +13089,14 @@
       <c r="P34" s="9"/>
       <c r="Q34" s="10"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="14"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -10609,17 +13115,17 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="5"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A40" s="6"/>
       <c r="D40" s="7"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A41" s="6"/>
       <c r="D41" s="7"/>
       <c r="Q41" s="7"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A42" s="6"/>
       <c r="D42" s="7"/>
       <c r="J42" t="s">
@@ -10627,27 +13133,27 @@
       </c>
       <c r="Q42" s="7"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A43" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D43" s="7"/>
       <c r="Q43" s="7"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D44" s="7"/>
       <c r="Q44" s="7"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A45" s="6"/>
       <c r="D45" s="7"/>
       <c r="Q45" s="7"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D46" s="7"/>
       <c r="Q46" s="7"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A47" s="13" t="s">
         <v>15</v>
       </c>
@@ -10657,27 +13163,27 @@
       </c>
       <c r="Q47" s="7"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D48" s="7"/>
       <c r="Q48" s="7"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A49" s="6"/>
       <c r="D49" s="7"/>
       <c r="Q49" s="7"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D50" s="7"/>
       <c r="Q50" s="7"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A51" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="7"/>
       <c r="Q51" s="7"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A52" s="6"/>
       <c r="D52" s="7"/>
       <c r="H52" t="s">
@@ -10685,26 +13191,26 @@
       </c>
       <c r="Q52" s="7"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A53" s="6"/>
       <c r="D53" s="7"/>
       <c r="Q53" s="7"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A54" s="6"/>
       <c r="D54" s="7"/>
       <c r="Q54" s="7"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D55" s="7"/>
       <c r="Q55" s="7"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A56" s="6"/>
       <c r="D56" s="7"/>
       <c r="Q56" s="7"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A57" s="6"/>
       <c r="D57" s="7"/>
       <c r="I57" t="s">
@@ -10712,37 +13218,37 @@
       </c>
       <c r="Q57" s="7"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A58" s="6"/>
       <c r="D58" s="7"/>
       <c r="Q58" s="7"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A59" s="6"/>
       <c r="D59" s="7"/>
       <c r="Q59" s="7"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A60" s="6"/>
       <c r="D60" s="7"/>
       <c r="Q60" s="7"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A61" s="6"/>
       <c r="D61" s="7"/>
       <c r="Q61" s="7"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A62" s="6"/>
       <c r="D62" s="7"/>
       <c r="Q62" s="7"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A63" s="6"/>
       <c r="D63" s="7"/>
       <c r="Q63" s="7"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A64" s="8"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
@@ -10761,14 +13267,14 @@
       <c r="P64" s="9"/>
       <c r="Q64" s="10"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="14"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A68" s="3"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -10787,17 +13293,17 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="5"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A69" s="6"/>
       <c r="D69" s="7"/>
       <c r="Q69" s="7"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A70" s="6"/>
       <c r="D70" s="7"/>
       <c r="Q70" s="7"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A71" s="6"/>
       <c r="D71" s="7"/>
       <c r="J71" t="s">
@@ -10805,18 +13311,18 @@
       </c>
       <c r="Q71" s="7"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A72" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D72" s="7"/>
       <c r="Q72" s="7"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D73" s="7"/>
       <c r="Q73" s="7"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A74" s="6"/>
       <c r="D74" s="7"/>
       <c r="I74" s="16" t="s">
@@ -10824,11 +13330,11 @@
       </c>
       <c r="Q74" s="7"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D75" s="7"/>
       <c r="Q75" s="7"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A76" s="13" t="s">
         <v>15</v>
       </c>
@@ -10838,27 +13344,27 @@
       </c>
       <c r="Q76" s="7"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D77" s="7"/>
       <c r="Q77" s="7"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A78" s="6"/>
       <c r="D78" s="7"/>
       <c r="Q78" s="7"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D79" s="7"/>
       <c r="Q79" s="7"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A80" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D80" s="7"/>
       <c r="Q80" s="7"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A81" s="6"/>
       <c r="D81" s="7"/>
       <c r="H81" t="s">
@@ -10866,46 +13372,46 @@
       </c>
       <c r="Q81" s="7"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A82" s="6"/>
       <c r="D82" s="7"/>
       <c r="Q82" s="7"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A83" s="6"/>
       <c r="D83" s="7"/>
       <c r="Q83" s="7"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D84" s="7"/>
       <c r="Q84" s="7"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A85" s="6"/>
       <c r="D85" s="7"/>
       <c r="Q85" s="7"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A86" s="6"/>
       <c r="D86" s="7"/>
       <c r="Q86" s="7"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A87" s="6"/>
       <c r="D87" s="7"/>
       <c r="Q87" s="7"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A88" s="6"/>
       <c r="D88" s="7"/>
       <c r="Q88" s="7"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A89" s="6"/>
       <c r="D89" s="7"/>
       <c r="Q89" s="7"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A90" s="6"/>
       <c r="D90" s="7"/>
       <c r="I90" t="s">
@@ -10913,17 +13419,17 @@
       </c>
       <c r="Q90" s="7"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A91" s="6"/>
       <c r="D91" s="7"/>
       <c r="Q91" s="7"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A92" s="6"/>
       <c r="D92" s="7"/>
       <c r="Q92" s="7"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A93" s="8"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
@@ -10942,7 +13448,7 @@
       <c r="P93" s="9"/>
       <c r="Q93" s="10"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
         <v>25</v>
       </c>
@@ -10950,7 +13456,7 @@
       <c r="C96" s="17"/>
       <c r="D96" s="14"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A97" s="3"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -10969,17 +13475,17 @@
       <c r="P97" s="4"/>
       <c r="Q97" s="5"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A98" s="6"/>
       <c r="D98" s="7"/>
       <c r="Q98" s="7"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A99" s="6"/>
       <c r="D99" s="7"/>
       <c r="Q99" s="7"/>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A100" s="6"/>
       <c r="D100" s="7"/>
       <c r="J100" t="s">
@@ -10987,28 +13493,28 @@
       </c>
       <c r="Q100" s="7"/>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A101" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D101" s="7"/>
       <c r="Q101" s="7"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D102" s="7"/>
       <c r="Q102" s="7"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A103" s="6"/>
       <c r="D103" s="7"/>
       <c r="I103" s="16"/>
       <c r="Q103" s="7"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D104" s="7"/>
       <c r="Q104" s="7"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A105" s="13" t="s">
         <v>15</v>
       </c>
@@ -11018,27 +13524,27 @@
       </c>
       <c r="Q105" s="7"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D106" s="7"/>
       <c r="Q106" s="7"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A107" s="6"/>
       <c r="D107" s="7"/>
       <c r="Q107" s="7"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D108" s="7"/>
       <c r="Q108" s="7"/>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A109" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D109" s="7"/>
       <c r="Q109" s="7"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A110" s="6"/>
       <c r="D110" s="7"/>
       <c r="H110" t="s">
@@ -11046,46 +13552,46 @@
       </c>
       <c r="Q110" s="7"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A111" s="6"/>
       <c r="D111" s="7"/>
       <c r="Q111" s="7"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A112" s="6"/>
       <c r="D112" s="7"/>
       <c r="Q112" s="7"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D113" s="7"/>
       <c r="Q113" s="7"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A114" s="6"/>
       <c r="D114" s="7"/>
       <c r="Q114" s="7"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A115" s="6"/>
       <c r="D115" s="7"/>
       <c r="Q115" s="7"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A116" s="6"/>
       <c r="D116" s="7"/>
       <c r="Q116" s="7"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A117" s="6"/>
       <c r="D117" s="7"/>
       <c r="Q117" s="7"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A118" s="6"/>
       <c r="D118" s="7"/>
       <c r="Q118" s="7"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A119" s="6"/>
       <c r="D119" s="7"/>
       <c r="I119" t="s">
@@ -11093,17 +13599,17 @@
       </c>
       <c r="Q119" s="7"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A120" s="6"/>
       <c r="D120" s="7"/>
       <c r="Q120" s="7"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A121" s="6"/>
       <c r="D121" s="7"/>
       <c r="Q121" s="7"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A122" s="8"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
@@ -11131,13 +13637,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85C61EA8-8183-45D7-BB3E-784982864B64}">
-  <dimension ref="A1:Q150"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:BB150"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -11163,7 +13672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>61</v>
@@ -11175,19 +13684,19 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="14"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>25</v>
       </c>
@@ -11195,7 +13704,7 @@
       <c r="C8" s="17"/>
       <c r="D8" s="14"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -11214,17 +13723,17 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="D10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="D11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="D12" s="7"/>
       <c r="J12" t="s">
@@ -11232,28 +13741,28 @@
       </c>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="D15" s="7"/>
       <c r="I15" s="16"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>15</v>
       </c>
@@ -11263,86 +13772,86 @@
       </c>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="D19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
       <c r="D22" s="7"/>
       <c r="Q22" s="7"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
       <c r="D23" s="7"/>
       <c r="Q23" s="7"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="6"/>
       <c r="D24" s="7"/>
       <c r="Q24" s="7"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D25" s="7"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="6"/>
       <c r="D26" s="7"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="6"/>
       <c r="D27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="6"/>
       <c r="D28" s="7"/>
       <c r="Q28" s="7"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="6"/>
       <c r="D29" s="7"/>
       <c r="Q29" s="7"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="6"/>
       <c r="D30" s="7"/>
       <c r="Q30" s="7"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="6"/>
       <c r="D31" s="7"/>
       <c r="Q31" s="7"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="6"/>
       <c r="D32" s="7"/>
       <c r="Q32" s="7"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A33" s="6"/>
       <c r="D33" s="7"/>
       <c r="Q33" s="7"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -11361,7 +13870,7 @@
       <c r="P34" s="9"/>
       <c r="Q34" s="10"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>28</v>
       </c>
@@ -11369,8 +13878,15 @@
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
       <c r="E37" s="14"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S37" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="T37" s="21"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="22"/>
+      <c r="W37" s="19"/>
+    </row>
+    <row r="38" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -11388,47 +13904,92 @@
       <c r="O38" s="4"/>
       <c r="P38" s="4"/>
       <c r="Q38" s="5"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S38" s="3"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="4"/>
+      <c r="AC38" s="4"/>
+      <c r="AD38" s="4"/>
+      <c r="AE38" s="4"/>
+      <c r="AF38" s="4"/>
+      <c r="AG38" s="4"/>
+      <c r="AH38" s="4"/>
+      <c r="AI38" s="5"/>
+    </row>
+    <row r="39" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A39" s="6"/>
       <c r="D39" s="7"/>
       <c r="Q39" s="7"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S39" s="6"/>
+      <c r="V39" s="7"/>
+      <c r="AI39" s="7"/>
+    </row>
+    <row r="40" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A40" s="6"/>
       <c r="D40" s="7"/>
       <c r="Q40" s="7"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S40" s="6"/>
+      <c r="V40" s="7"/>
+      <c r="AI40" s="7"/>
+    </row>
+    <row r="41" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A41" s="6"/>
       <c r="D41" s="7"/>
       <c r="J41" t="s">
         <v>26</v>
       </c>
       <c r="Q41" s="7"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S41" s="6"/>
+      <c r="V41" s="7"/>
+      <c r="AB41" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI41" s="7"/>
+    </row>
+    <row r="42" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A42" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D42" s="7"/>
       <c r="Q42" s="7"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V42" s="7"/>
+      <c r="AI42" s="7"/>
+    </row>
+    <row r="43" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D43" s="7"/>
       <c r="Q43" s="7"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V43" s="7"/>
+      <c r="AI43" s="7"/>
+    </row>
+    <row r="44" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A44" s="6"/>
       <c r="D44" s="7"/>
       <c r="I44" s="16"/>
       <c r="Q44" s="7"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S44" s="6"/>
+      <c r="V44" s="7"/>
+      <c r="Z44" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA44" s="16"/>
+      <c r="AI44" s="7"/>
+    </row>
+    <row r="45" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D45" s="7"/>
       <c r="Q45" s="7"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V45" s="7"/>
+      <c r="AI45" s="7"/>
+    </row>
+    <row r="46" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A46" s="13" t="s">
         <v>15</v>
       </c>
@@ -11437,90 +13998,148 @@
         <v>27</v>
       </c>
       <c r="Q46" s="7"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S46" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="V46" s="7"/>
+      <c r="Z46" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI46" s="7"/>
+    </row>
+    <row r="47" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D47" s="7"/>
       <c r="Q47" s="7"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V47" s="7"/>
+      <c r="AI47" s="7"/>
+    </row>
+    <row r="48" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A48" s="6"/>
       <c r="D48" s="7"/>
       <c r="Q48" s="7"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S48" s="6"/>
+      <c r="V48" s="7"/>
+      <c r="AI48" s="7"/>
+    </row>
+    <row r="49" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D49" s="7"/>
       <c r="Q49" s="7"/>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V49" s="7"/>
+      <c r="AI49" s="7"/>
+    </row>
+    <row r="50" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A50" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="7"/>
       <c r="Q50" s="7"/>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S50" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="V50" s="7"/>
+      <c r="AI50" s="7"/>
+    </row>
+    <row r="51" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A51" s="6"/>
       <c r="D51" s="7"/>
       <c r="Q51" s="7"/>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S51" s="6"/>
+      <c r="V51" s="7"/>
+      <c r="AI51" s="7"/>
+    </row>
+    <row r="52" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A52" s="6"/>
       <c r="D52" s="7"/>
       <c r="Q52" s="7"/>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S52" s="6"/>
+      <c r="V52" s="7"/>
+      <c r="AI52" s="7"/>
+    </row>
+    <row r="53" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A53" s="6"/>
       <c r="D53" s="7"/>
       <c r="Q53" s="7"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S53" s="6"/>
+      <c r="V53" s="7"/>
+      <c r="AI53" s="7"/>
+    </row>
+    <row r="54" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D54" s="7"/>
       <c r="Q54" s="7"/>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V54" s="7"/>
+      <c r="AI54" s="7"/>
+    </row>
+    <row r="55" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A55" s="6"/>
       <c r="D55" s="7"/>
       <c r="I55" s="11" t="s">
         <v>29</v>
       </c>
       <c r="Q55" s="7"/>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S55" s="6"/>
+      <c r="V55" s="7"/>
+      <c r="AA55" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI55" s="7"/>
+    </row>
+    <row r="56" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A56" s="6"/>
       <c r="D56" s="7"/>
       <c r="Q56" s="7"/>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S56" s="6"/>
+      <c r="V56" s="7"/>
+      <c r="AI56" s="7"/>
+    </row>
+    <row r="57" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A57" s="6"/>
       <c r="D57" s="7"/>
       <c r="Q57" s="7"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S57" s="6"/>
+      <c r="V57" s="7"/>
+      <c r="AI57" s="7"/>
+    </row>
+    <row r="58" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A58" s="6"/>
       <c r="D58" s="7"/>
       <c r="Q58" s="7"/>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S58" s="6"/>
+      <c r="V58" s="7"/>
+      <c r="AI58" s="7"/>
+    </row>
+    <row r="59" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A59" s="6"/>
       <c r="D59" s="7"/>
       <c r="Q59" s="7"/>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S59" s="6"/>
+      <c r="V59" s="7"/>
+      <c r="AI59" s="7"/>
+    </row>
+    <row r="60" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A60" s="6"/>
       <c r="D60" s="7"/>
       <c r="Q60" s="7"/>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S60" s="6"/>
+      <c r="V60" s="7"/>
+      <c r="AI60" s="7"/>
+    </row>
+    <row r="61" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A61" s="6"/>
       <c r="D61" s="7"/>
       <c r="Q61" s="7"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S61" s="6"/>
+      <c r="V61" s="7"/>
+      <c r="AI61" s="7"/>
+    </row>
+    <row r="62" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A62" s="6"/>
       <c r="D62" s="7"/>
       <c r="Q62" s="7"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S62" s="6"/>
+      <c r="V62" s="7"/>
+      <c r="AI62" s="7"/>
+    </row>
+    <row r="63" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -11538,16 +14157,47 @@
       <c r="O63" s="9"/>
       <c r="P63" s="9"/>
       <c r="Q63" s="10"/>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S63" s="8"/>
+      <c r="T63" s="9"/>
+      <c r="U63" s="9"/>
+      <c r="V63" s="10"/>
+      <c r="W63" s="9"/>
+      <c r="X63" s="9"/>
+      <c r="Y63" s="9"/>
+      <c r="Z63" s="9"/>
+      <c r="AA63" s="9"/>
+      <c r="AB63" s="9"/>
+      <c r="AC63" s="9"/>
+      <c r="AD63" s="9"/>
+      <c r="AE63" s="9"/>
+      <c r="AF63" s="9"/>
+      <c r="AG63" s="9"/>
+      <c r="AH63" s="9"/>
+      <c r="AI63" s="10"/>
+    </row>
+    <row r="66" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="17"/>
       <c r="D66" s="14"/>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S66" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="T66" s="21"/>
+      <c r="U66" s="22"/>
+      <c r="V66" s="22"/>
+      <c r="W66" s="19"/>
+      <c r="AL66" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM66" s="21"/>
+      <c r="AN66" s="22"/>
+      <c r="AO66" s="22"/>
+      <c r="AP66" s="19"/>
+    </row>
+    <row r="67" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A67" s="3"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -11565,137 +14215,336 @@
       <c r="O67" s="4"/>
       <c r="P67" s="4"/>
       <c r="Q67" s="5"/>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S67" s="3"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="5"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="4"/>
+      <c r="AD67" s="4"/>
+      <c r="AE67" s="4"/>
+      <c r="AF67" s="4"/>
+      <c r="AG67" s="4"/>
+      <c r="AH67" s="4"/>
+      <c r="AI67" s="5"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="4"/>
+      <c r="AN67" s="4"/>
+      <c r="AO67" s="5"/>
+      <c r="AP67" s="4"/>
+      <c r="AQ67" s="4"/>
+      <c r="AR67" s="4"/>
+      <c r="AS67" s="4"/>
+      <c r="AT67" s="4"/>
+      <c r="AU67" s="4"/>
+      <c r="AV67" s="4"/>
+      <c r="AW67" s="4"/>
+      <c r="AX67" s="4"/>
+      <c r="AY67" s="4"/>
+      <c r="AZ67" s="4"/>
+      <c r="BA67" s="4"/>
+      <c r="BB67" s="5"/>
+    </row>
+    <row r="68" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A68" s="6"/>
       <c r="D68" s="7"/>
       <c r="Q68" s="7"/>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S68" s="6"/>
+      <c r="V68" s="7"/>
+      <c r="AI68" s="7"/>
+      <c r="AL68" s="6"/>
+      <c r="AO68" s="7"/>
+      <c r="BB68" s="7"/>
+    </row>
+    <row r="69" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A69" s="6"/>
       <c r="D69" s="7"/>
       <c r="Q69" s="7"/>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S69" s="6"/>
+      <c r="V69" s="7"/>
+      <c r="AI69" s="7"/>
+      <c r="AL69" s="6"/>
+      <c r="AO69" s="7"/>
+      <c r="BB69" s="7"/>
+    </row>
+    <row r="70" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A70" s="6"/>
       <c r="D70" s="7"/>
       <c r="J70" t="s">
         <v>26</v>
       </c>
       <c r="Q70" s="7"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S70" s="6"/>
+      <c r="V70" s="7"/>
+      <c r="AB70" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI70" s="7"/>
+      <c r="AL70" s="6"/>
+      <c r="AO70" s="7"/>
+      <c r="AU70" t="s">
+        <v>26</v>
+      </c>
+      <c r="BB70" s="7"/>
+    </row>
+    <row r="71" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A71" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D71" s="7"/>
       <c r="Q71" s="7"/>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S71" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V71" s="7"/>
+      <c r="AI71" s="7"/>
+      <c r="AL71" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO71" s="7"/>
+      <c r="BB71" s="7"/>
+    </row>
+    <row r="72" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D72" s="7"/>
       <c r="Q72" s="7"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V72" s="7"/>
+      <c r="AI72" s="7"/>
+      <c r="AO72" s="7"/>
+      <c r="BB72" s="7"/>
+    </row>
+    <row r="73" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A73" s="6"/>
       <c r="D73" s="7"/>
       <c r="I73" s="16"/>
       <c r="Q73" s="7"/>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S73" s="6"/>
+      <c r="V73" s="7"/>
+      <c r="AA73" s="16"/>
+      <c r="AI73" s="7"/>
+      <c r="AL73" s="6"/>
+      <c r="AO73" s="7"/>
+      <c r="AS73" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="AT73" s="16"/>
+      <c r="BB73" s="7"/>
+    </row>
+    <row r="74" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D74" s="7"/>
       <c r="Q74" s="7"/>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V74" s="7"/>
+      <c r="AI74" s="7"/>
+      <c r="AO74" s="7"/>
+      <c r="BB74" s="7"/>
+    </row>
+    <row r="75" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A75" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="7"/>
       <c r="Q75" s="7"/>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S75" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="V75" s="7"/>
+      <c r="Z75" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI75" s="7"/>
+      <c r="AL75" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO75" s="7"/>
+      <c r="AS75" t="s">
+        <v>68</v>
+      </c>
+      <c r="BB75" s="7"/>
+    </row>
+    <row r="76" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D76" s="7"/>
       <c r="H76" t="s">
         <v>31</v>
       </c>
       <c r="Q76" s="7"/>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V76" s="7"/>
+      <c r="AI76" s="7"/>
+      <c r="AO76" s="7"/>
+      <c r="BB76" s="7"/>
+    </row>
+    <row r="77" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A77" s="6"/>
       <c r="D77" s="7"/>
       <c r="Q77" s="7"/>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S77" s="6"/>
+      <c r="V77" s="7"/>
+      <c r="AI77" s="7"/>
+      <c r="AL77" s="6"/>
+      <c r="AO77" s="7"/>
+      <c r="BB77" s="7"/>
+    </row>
+    <row r="78" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D78" s="7"/>
       <c r="Q78" s="7"/>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V78" s="7"/>
+      <c r="AI78" s="7"/>
+      <c r="AO78" s="7"/>
+      <c r="BB78" s="7"/>
+    </row>
+    <row r="79" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A79" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D79" s="7"/>
       <c r="Q79" s="7"/>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="V79" s="7"/>
+      <c r="AI79" s="7"/>
+      <c r="AL79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO79" s="7"/>
+      <c r="BB79" s="7"/>
+    </row>
+    <row r="80" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A80" s="6"/>
       <c r="D80" s="7"/>
       <c r="Q80" s="7"/>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S80" s="6"/>
+      <c r="V80" s="7"/>
+      <c r="AI80" s="7"/>
+      <c r="AL80" s="6"/>
+      <c r="AO80" s="7"/>
+      <c r="BB80" s="7"/>
+    </row>
+    <row r="81" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A81" s="6"/>
       <c r="D81" s="7"/>
       <c r="Q81" s="7"/>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S81" s="6"/>
+      <c r="V81" s="7"/>
+      <c r="AI81" s="7"/>
+      <c r="AL81" s="6"/>
+      <c r="AO81" s="7"/>
+      <c r="BB81" s="7"/>
+    </row>
+    <row r="82" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A82" s="6"/>
       <c r="D82" s="7"/>
       <c r="Q82" s="7"/>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S82" s="6"/>
+      <c r="V82" s="7"/>
+      <c r="AI82" s="7"/>
+      <c r="AL82" s="6"/>
+      <c r="AO82" s="7"/>
+      <c r="BB82" s="7"/>
+    </row>
+    <row r="83" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D83" s="7"/>
       <c r="Q83" s="7"/>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V83" s="7"/>
+      <c r="AI83" s="7"/>
+      <c r="AO83" s="7"/>
+      <c r="BB83" s="7"/>
+    </row>
+    <row r="84" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A84" s="6"/>
       <c r="D84" s="7"/>
       <c r="I84" s="11"/>
       <c r="Q84" s="7"/>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S84" s="6"/>
+      <c r="V84" s="7"/>
+      <c r="AA84" s="11"/>
+      <c r="AI84" s="7"/>
+      <c r="AL84" s="6"/>
+      <c r="AO84" s="7"/>
+      <c r="AT84" s="11"/>
+      <c r="BB84" s="7"/>
+    </row>
+    <row r="85" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A85" s="6"/>
       <c r="D85" s="7"/>
       <c r="Q85" s="7"/>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S85" s="6"/>
+      <c r="V85" s="7"/>
+      <c r="AI85" s="7"/>
+      <c r="AL85" s="6"/>
+      <c r="AO85" s="7"/>
+      <c r="BB85" s="7"/>
+    </row>
+    <row r="86" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A86" s="6"/>
       <c r="D86" s="7"/>
       <c r="Q86" s="7"/>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S86" s="6"/>
+      <c r="V86" s="7"/>
+      <c r="AI86" s="7"/>
+      <c r="AL86" s="6"/>
+      <c r="AO86" s="7"/>
+      <c r="BB86" s="7"/>
+    </row>
+    <row r="87" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A87" s="6"/>
       <c r="D87" s="7"/>
       <c r="Q87" s="7"/>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S87" s="6"/>
+      <c r="V87" s="7"/>
+      <c r="AI87" s="7"/>
+      <c r="AL87" s="6"/>
+      <c r="AO87" s="7"/>
+      <c r="BB87" s="7"/>
+    </row>
+    <row r="88" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A88" s="6"/>
       <c r="D88" s="7"/>
       <c r="Q88" s="7"/>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S88" s="6"/>
+      <c r="V88" s="7"/>
+      <c r="AI88" s="7"/>
+      <c r="AL88" s="6"/>
+      <c r="AO88" s="7"/>
+      <c r="BB88" s="7"/>
+    </row>
+    <row r="89" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A89" s="6"/>
       <c r="D89" s="7"/>
       <c r="Q89" s="7"/>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S89" s="6"/>
+      <c r="V89" s="7"/>
+      <c r="AI89" s="7"/>
+      <c r="AL89" s="6"/>
+      <c r="AO89" s="7"/>
+      <c r="BB89" s="7"/>
+    </row>
+    <row r="90" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A90" s="6"/>
       <c r="D90" s="7"/>
       <c r="Q90" s="7"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S90" s="6"/>
+      <c r="V90" s="7"/>
+      <c r="AI90" s="7"/>
+      <c r="AL90" s="6"/>
+      <c r="AO90" s="7"/>
+      <c r="BB90" s="7"/>
+    </row>
+    <row r="91" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A91" s="6"/>
       <c r="D91" s="7"/>
       <c r="Q91" s="7"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S91" s="6"/>
+      <c r="V91" s="7"/>
+      <c r="AI91" s="7"/>
+      <c r="AL91" s="6"/>
+      <c r="AO91" s="7"/>
+      <c r="BB91" s="7"/>
+    </row>
+    <row r="92" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A92" s="8"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
@@ -11713,16 +14562,58 @@
       <c r="O92" s="9"/>
       <c r="P92" s="9"/>
       <c r="Q92" s="10"/>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S92" s="8"/>
+      <c r="T92" s="9"/>
+      <c r="U92" s="9"/>
+      <c r="V92" s="10"/>
+      <c r="W92" s="9"/>
+      <c r="X92" s="9"/>
+      <c r="Y92" s="9"/>
+      <c r="Z92" s="9"/>
+      <c r="AA92" s="9"/>
+      <c r="AB92" s="9"/>
+      <c r="AC92" s="9"/>
+      <c r="AD92" s="9"/>
+      <c r="AE92" s="9"/>
+      <c r="AF92" s="9"/>
+      <c r="AG92" s="9"/>
+      <c r="AH92" s="9"/>
+      <c r="AI92" s="10"/>
+      <c r="AL92" s="8"/>
+      <c r="AM92" s="9"/>
+      <c r="AN92" s="9"/>
+      <c r="AO92" s="10"/>
+      <c r="AP92" s="9"/>
+      <c r="AQ92" s="9"/>
+      <c r="AR92" s="9"/>
+      <c r="AS92" s="9"/>
+      <c r="AT92" s="9"/>
+      <c r="AU92" s="9"/>
+      <c r="AV92" s="9"/>
+      <c r="AW92" s="9"/>
+      <c r="AX92" s="9"/>
+      <c r="AY92" s="9"/>
+      <c r="AZ92" s="9"/>
+      <c r="BA92" s="9"/>
+      <c r="BB92" s="10"/>
+    </row>
+    <row r="95" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A95" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="17"/>
       <c r="D95" s="14"/>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S95" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="T95" s="21"/>
+      <c r="U95" s="22"/>
+      <c r="V95" s="19"/>
+      <c r="W95" s="22"/>
+      <c r="X95" s="19"/>
+    </row>
+    <row r="96" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A96" s="3"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -11740,37 +14631,73 @@
       <c r="O96" s="4"/>
       <c r="P96" s="4"/>
       <c r="Q96" s="5"/>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S96" s="3"/>
+      <c r="T96" s="4"/>
+      <c r="U96" s="4"/>
+      <c r="V96" s="5"/>
+      <c r="W96" s="4"/>
+      <c r="X96" s="4"/>
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="4"/>
+      <c r="AA96" s="4"/>
+      <c r="AB96" s="4"/>
+      <c r="AC96" s="4"/>
+      <c r="AD96" s="4"/>
+      <c r="AE96" s="4"/>
+      <c r="AF96" s="4"/>
+      <c r="AG96" s="4"/>
+      <c r="AH96" s="4"/>
+      <c r="AI96" s="5"/>
+    </row>
+    <row r="97" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A97" s="6"/>
       <c r="D97" s="7"/>
       <c r="Q97" s="7"/>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S97" s="6"/>
+      <c r="V97" s="7"/>
+      <c r="AI97" s="7"/>
+    </row>
+    <row r="98" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A98" s="6"/>
       <c r="D98" s="7"/>
       <c r="Q98" s="7"/>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S98" s="6"/>
+      <c r="V98" s="7"/>
+      <c r="AI98" s="7"/>
+    </row>
+    <row r="99" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A99" s="6"/>
       <c r="D99" s="7"/>
       <c r="J99" t="s">
         <v>26</v>
       </c>
       <c r="Q99" s="7"/>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S99" s="6"/>
+      <c r="V99" s="7"/>
+      <c r="AB99" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI99" s="7"/>
+    </row>
+    <row r="100" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A100" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D100" s="7"/>
       <c r="Q100" s="7"/>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S100" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V100" s="7"/>
+      <c r="AI100" s="7"/>
+    </row>
+    <row r="101" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D101" s="7"/>
       <c r="Q101" s="7"/>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V101" s="7"/>
+      <c r="AI101" s="7"/>
+    </row>
+    <row r="102" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A102" s="6"/>
       <c r="D102" s="7"/>
       <c r="H102" t="s">
@@ -11778,102 +14705,164 @@
       </c>
       <c r="I102" s="16"/>
       <c r="Q102" s="7"/>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S102" s="6"/>
+      <c r="V102" s="7"/>
+      <c r="AA102" s="16"/>
+      <c r="AI102" s="7"/>
+    </row>
+    <row r="103" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D103" s="7"/>
       <c r="Q103" s="7"/>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V103" s="7"/>
+      <c r="AI103" s="7"/>
+    </row>
+    <row r="104" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A104" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D104" s="7"/>
       <c r="Q104" s="7"/>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S104" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="V104" s="7"/>
+      <c r="AI104" s="7"/>
+    </row>
+    <row r="105" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D105" s="7"/>
       <c r="Q105" s="7"/>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V105" s="7"/>
+      <c r="Z105" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI105" s="7"/>
+    </row>
+    <row r="106" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A106" s="6"/>
       <c r="D106" s="7"/>
       <c r="Q106" s="7"/>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S106" s="6"/>
+      <c r="V106" s="7"/>
+      <c r="AI106" s="7"/>
+    </row>
+    <row r="107" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D107" s="7"/>
       <c r="H107" t="s">
         <v>32</v>
       </c>
       <c r="Q107" s="7"/>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V107" s="7"/>
+      <c r="AI107" s="7"/>
+    </row>
+    <row r="108" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A108" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D108" s="7"/>
       <c r="Q108" s="7"/>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S108" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="V108" s="7"/>
+      <c r="AI108" s="7"/>
+    </row>
+    <row r="109" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A109" s="6"/>
       <c r="D109" s="7"/>
       <c r="Q109" s="7"/>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S109" s="6"/>
+      <c r="V109" s="7"/>
+      <c r="AI109" s="7"/>
+    </row>
+    <row r="110" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A110" s="6"/>
       <c r="D110" s="7"/>
       <c r="Q110" s="7"/>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S110" s="6"/>
+      <c r="V110" s="7"/>
+      <c r="AI110" s="7"/>
+    </row>
+    <row r="111" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A111" s="6"/>
       <c r="D111" s="7"/>
       <c r="Q111" s="7"/>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S111" s="6"/>
+      <c r="V111" s="7"/>
+      <c r="AI111" s="7"/>
+    </row>
+    <row r="112" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D112" s="7"/>
       <c r="Q112" s="7"/>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="V112" s="7"/>
+      <c r="AI112" s="7"/>
+    </row>
+    <row r="113" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A113" s="6"/>
       <c r="D113" s="7"/>
       <c r="I113" s="11"/>
       <c r="Q113" s="7"/>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S113" s="6"/>
+      <c r="V113" s="7"/>
+      <c r="AA113" s="11"/>
+      <c r="AI113" s="7"/>
+    </row>
+    <row r="114" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A114" s="6"/>
       <c r="D114" s="7"/>
       <c r="Q114" s="7"/>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S114" s="6"/>
+      <c r="V114" s="7"/>
+      <c r="AI114" s="7"/>
+    </row>
+    <row r="115" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A115" s="6"/>
       <c r="D115" s="7"/>
       <c r="Q115" s="7"/>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S115" s="6"/>
+      <c r="V115" s="7"/>
+      <c r="AI115" s="7"/>
+    </row>
+    <row r="116" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A116" s="6"/>
       <c r="D116" s="7"/>
       <c r="Q116" s="7"/>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S116" s="6"/>
+      <c r="V116" s="7"/>
+      <c r="AI116" s="7"/>
+    </row>
+    <row r="117" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A117" s="6"/>
       <c r="D117" s="7"/>
       <c r="Q117" s="7"/>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S117" s="6"/>
+      <c r="V117" s="7"/>
+      <c r="AI117" s="7"/>
+    </row>
+    <row r="118" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A118" s="6"/>
       <c r="D118" s="7"/>
       <c r="Q118" s="7"/>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S118" s="6"/>
+      <c r="V118" s="7"/>
+      <c r="AI118" s="7"/>
+    </row>
+    <row r="119" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A119" s="6"/>
       <c r="D119" s="7"/>
       <c r="Q119" s="7"/>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S119" s="6"/>
+      <c r="V119" s="7"/>
+      <c r="AI119" s="7"/>
+    </row>
+    <row r="120" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A120" s="6"/>
       <c r="D120" s="7"/>
       <c r="Q120" s="7"/>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S120" s="6"/>
+      <c r="V120" s="7"/>
+      <c r="AI120" s="7"/>
+    </row>
+    <row r="121" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A121" s="8"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
@@ -11891,8 +14880,25 @@
       <c r="O121" s="9"/>
       <c r="P121" s="9"/>
       <c r="Q121" s="10"/>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="S121" s="8"/>
+      <c r="T121" s="9"/>
+      <c r="U121" s="9"/>
+      <c r="V121" s="10"/>
+      <c r="W121" s="9"/>
+      <c r="X121" s="9"/>
+      <c r="Y121" s="9"/>
+      <c r="Z121" s="9"/>
+      <c r="AA121" s="9"/>
+      <c r="AB121" s="9"/>
+      <c r="AC121" s="9"/>
+      <c r="AD121" s="9"/>
+      <c r="AE121" s="9"/>
+      <c r="AF121" s="9"/>
+      <c r="AG121" s="9"/>
+      <c r="AH121" s="9"/>
+      <c r="AI121" s="10"/>
+    </row>
+    <row r="124" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A124" s="1" t="s">
         <v>34</v>
       </c>
@@ -11900,7 +14906,7 @@
       <c r="C124" s="17"/>
       <c r="D124" s="14"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A125" s="3"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -11919,17 +14925,17 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="5"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A126" s="6"/>
       <c r="D126" s="7"/>
       <c r="Q126" s="7"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A127" s="6"/>
       <c r="D127" s="7"/>
       <c r="Q127" s="7"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A128" s="6"/>
       <c r="D128" s="7"/>
       <c r="J128" t="s">
@@ -11937,27 +14943,27 @@
       </c>
       <c r="Q128" s="7"/>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A129" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D129" s="7"/>
       <c r="Q129" s="7"/>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D130" s="7"/>
       <c r="Q130" s="7"/>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A131" s="6"/>
       <c r="D131" s="7"/>
       <c r="Q131" s="7"/>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D132" s="7"/>
       <c r="Q132" s="7"/>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A133" s="13" t="s">
         <v>15</v>
       </c>
@@ -11967,27 +14973,27 @@
       </c>
       <c r="Q133" s="7"/>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D134" s="7"/>
       <c r="Q134" s="7"/>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A135" s="6"/>
       <c r="D135" s="7"/>
       <c r="Q135" s="7"/>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D136" s="7"/>
       <c r="Q136" s="7"/>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A137" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D137" s="7"/>
       <c r="Q137" s="7"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A138" s="6"/>
       <c r="D138" s="7"/>
       <c r="H138" t="s">
@@ -11995,21 +15001,21 @@
       </c>
       <c r="Q138" s="7"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A139" s="6"/>
       <c r="D139" s="7"/>
       <c r="Q139" s="7"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A140" s="6"/>
       <c r="D140" s="7"/>
       <c r="Q140" s="7"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D141" s="7"/>
       <c r="Q141" s="7"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A142" s="6"/>
       <c r="D142" s="7"/>
       <c r="H142" t="s">
@@ -12017,42 +15023,42 @@
       </c>
       <c r="Q142" s="7"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A143" s="6"/>
       <c r="D143" s="7"/>
       <c r="Q143" s="7"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A144" s="6"/>
       <c r="D144" s="7"/>
       <c r="Q144" s="7"/>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A145" s="6"/>
       <c r="D145" s="7"/>
       <c r="Q145" s="7"/>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A146" s="6"/>
       <c r="D146" s="7"/>
       <c r="Q146" s="7"/>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A147" s="6"/>
       <c r="D147" s="7"/>
       <c r="Q147" s="7"/>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A148" s="6"/>
       <c r="D148" s="7"/>
       <c r="Q148" s="7"/>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A149" s="6"/>
       <c r="D149" s="7"/>
       <c r="Q149" s="7"/>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A150" s="8"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
@@ -12079,11 +15085,205 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AD4012-35B3-4B40-89BA-42BE701D6A04}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A2:Q28"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="5"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="Q4" s="7"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="Q7" s="7"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="D8" s="7"/>
+      <c r="Q8" s="7"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="Q9" s="7"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="D10" s="7"/>
+      <c r="Q10" s="7"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="7"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="D12" s="7"/>
+      <c r="Q12" s="7"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="Q13" s="7"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="D14" s="7"/>
+      <c r="Q14" s="7"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A15" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="Q15" s="7"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q16" s="7"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="Q17" s="7"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="Q18" s="7"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="D19" s="7"/>
+      <c r="Q19" s="7"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="H20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q20" s="7"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="Q21" s="7"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="Q22" s="7"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="Q23" s="7"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="Q24" s="7"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="Q25" s="7"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="Q26" s="7"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="Q27" s="7"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="10"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D7E4E4E-F305-43BF-B9D3-E3CA5455A637}">
   <dimension ref="A1:Q183"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -12109,7 +15309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -12121,25 +15321,25 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="14"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -12158,130 +15358,130 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="D10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="D11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="D12" s="7"/>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="D15" s="7"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="7"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="D19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
       <c r="D22" s="7"/>
       <c r="Q22" s="7"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
       <c r="D23" s="7"/>
       <c r="Q23" s="7"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="7"/>
       <c r="Q24" s="7"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D25" s="7"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="6"/>
       <c r="D26" s="7"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="6"/>
       <c r="D27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="6"/>
       <c r="D28" s="7"/>
       <c r="Q28" s="7"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="6"/>
       <c r="D29" s="7"/>
       <c r="Q29" s="7"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="6"/>
       <c r="D30" s="7"/>
       <c r="Q30" s="7"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="6"/>
       <c r="D31" s="7"/>
       <c r="Q31" s="7"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="6"/>
       <c r="D32" s="7"/>
       <c r="Q32" s="7"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A33" s="6"/>
       <c r="D33" s="7"/>
       <c r="Q33" s="7"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -12300,14 +15500,14 @@
       <c r="P34" s="9"/>
       <c r="Q34" s="10"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="14"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -12326,111 +15526,111 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="5"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A39" s="6"/>
       <c r="D39" s="7"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A40" s="6"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A41" s="6"/>
       <c r="Q41" s="7"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A42" s="12"/>
       <c r="Q42" s="7"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
         <v>39</v>
       </c>
       <c r="Q43" s="7"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A44" s="6"/>
       <c r="Q44" s="7"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q45" s="7"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A46" s="13"/>
       <c r="B46" t="s">
         <v>40</v>
       </c>
       <c r="Q46" s="7"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q47" s="7"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A48" s="6"/>
       <c r="Q48" s="7"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
         <v>41</v>
       </c>
       <c r="Q49" s="7"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A50" s="12"/>
       <c r="Q50" s="7"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A51" s="6"/>
       <c r="Q51" s="7"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A52" s="6"/>
       <c r="Q52" s="7"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A53" s="13"/>
       <c r="Q53" s="7"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q54" s="7"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A55" s="6"/>
       <c r="Q55" s="7"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A56" s="6"/>
       <c r="Q56" s="7"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A57" s="6"/>
       <c r="Q57" s="7"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A58" s="6"/>
       <c r="E58" t="s">
         <v>42</v>
       </c>
       <c r="Q58" s="7"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A59" s="6"/>
       <c r="Q59" s="7"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A60" s="6"/>
       <c r="Q60" s="7"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A61" s="6"/>
       <c r="Q61" s="7"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A62" s="6"/>
       <c r="Q62" s="7"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -12449,14 +15649,14 @@
       <c r="P63" s="9"/>
       <c r="Q63" s="10"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="14"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A68" s="3"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -12475,130 +15675,130 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="5"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A69" s="6"/>
       <c r="D69" s="7"/>
       <c r="Q69" s="7"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A70" s="6"/>
       <c r="D70" s="7"/>
       <c r="Q70" s="7"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A71" s="6"/>
       <c r="D71" s="7"/>
       <c r="Q71" s="7"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A72" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D72" s="7"/>
       <c r="Q72" s="7"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D73" s="7"/>
       <c r="Q73" s="7"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A74" s="6"/>
       <c r="D74" s="7"/>
       <c r="Q74" s="7"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D75" s="7"/>
       <c r="Q75" s="7"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A76" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="7"/>
       <c r="Q76" s="7"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D77" s="7"/>
       <c r="Q77" s="7"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A78" s="6"/>
       <c r="D78" s="7"/>
       <c r="Q78" s="7"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D79" s="7"/>
       <c r="Q79" s="7"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A80" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D80" s="7"/>
       <c r="Q80" s="7"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A81" s="6"/>
       <c r="D81" s="7"/>
       <c r="Q81" s="7"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A82" s="6"/>
       <c r="D82" s="7"/>
       <c r="Q82" s="7"/>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A83" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D83" s="7"/>
       <c r="Q83" s="7"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D84" s="7"/>
       <c r="Q84" s="7"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A85" s="6"/>
       <c r="D85" s="7"/>
       <c r="Q85" s="7"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A86" s="6"/>
       <c r="D86" s="7"/>
       <c r="Q86" s="7"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A87" s="6"/>
       <c r="D87" s="7"/>
       <c r="Q87" s="7"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A88" s="6"/>
       <c r="D88" s="7"/>
       <c r="Q88" s="7"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A89" s="6"/>
       <c r="D89" s="7"/>
       <c r="Q89" s="7"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A90" s="6"/>
       <c r="D90" s="7"/>
       <c r="Q90" s="7"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A91" s="6"/>
       <c r="D91" s="7"/>
       <c r="Q91" s="7"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A92" s="6"/>
       <c r="D92" s="7"/>
       <c r="Q92" s="7"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A93" s="8"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
@@ -12617,7 +15817,7 @@
       <c r="P93" s="9"/>
       <c r="Q93" s="10"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
         <v>44</v>
       </c>
@@ -12625,7 +15825,7 @@
       <c r="C97" s="17"/>
       <c r="D97" s="14"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A98" s="3"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -12644,126 +15844,126 @@
       <c r="P98" s="4"/>
       <c r="Q98" s="5"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A99" s="6"/>
       <c r="D99" s="7"/>
       <c r="Q99" s="7"/>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A100" s="6"/>
       <c r="Q100" s="7"/>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A101" s="6"/>
       <c r="Q101" s="7"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A102" s="12"/>
       <c r="Q102" s="7"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B103" t="s">
         <v>45</v>
       </c>
       <c r="Q103" s="7"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A104" s="6"/>
       <c r="Q104" s="7"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
       <c r="C105" t="s">
         <v>46</v>
       </c>
       <c r="Q105" s="7"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A106" s="13"/>
       <c r="C106" t="s">
         <v>47</v>
       </c>
       <c r="Q106" s="7"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q107" s="7"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A108" s="6"/>
       <c r="Q108" s="7"/>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B109" t="s">
         <v>48</v>
       </c>
       <c r="Q109" s="7"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A110" s="12"/>
       <c r="Q110" s="7"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A111" s="6"/>
       <c r="B111" t="s">
         <v>49</v>
       </c>
       <c r="Q111" s="7"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A112" s="6"/>
       <c r="Q112" s="7"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A113" s="13"/>
       <c r="Q113" s="7"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B114" t="s">
         <v>40</v>
       </c>
       <c r="Q114" s="7"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A115" s="6"/>
       <c r="Q115" s="7"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A116" s="6"/>
       <c r="B116" t="s">
         <v>51</v>
       </c>
       <c r="Q116" s="7"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A117" s="6"/>
       <c r="Q117" s="7"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A118" s="6"/>
       <c r="B118" t="s">
         <v>50</v>
       </c>
       <c r="Q118" s="7"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A119" s="6"/>
       <c r="Q119" s="7"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A120" s="6"/>
       <c r="Q120" s="7"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A121" s="6"/>
       <c r="B121" t="s">
         <v>52</v>
       </c>
       <c r="Q121" s="7"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A122" s="6"/>
       <c r="Q122" s="7"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A123" s="8"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
@@ -12782,7 +15982,7 @@
       <c r="P123" s="9"/>
       <c r="Q123" s="10"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A127" s="1" t="s">
         <v>53</v>
       </c>
@@ -12790,7 +15990,7 @@
       <c r="C127" s="17"/>
       <c r="D127" s="14"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A128" s="3"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -12809,130 +16009,130 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="5"/>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A129" s="6"/>
       <c r="D129" s="7"/>
       <c r="Q129" s="7"/>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A130" s="6"/>
       <c r="D130" s="7"/>
       <c r="Q130" s="7"/>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A131" s="6"/>
       <c r="D131" s="7"/>
       <c r="Q131" s="7"/>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A132" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D132" s="7"/>
       <c r="Q132" s="7"/>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D133" s="7"/>
       <c r="Q133" s="7"/>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A134" s="6"/>
       <c r="D134" s="7"/>
       <c r="Q134" s="7"/>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D135" s="7"/>
       <c r="Q135" s="7"/>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A136" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D136" s="7"/>
       <c r="Q136" s="7"/>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D137" s="7"/>
       <c r="Q137" s="7"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A138" s="6"/>
       <c r="D138" s="7"/>
       <c r="Q138" s="7"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D139" s="7"/>
       <c r="Q139" s="7"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A140" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D140" s="7"/>
       <c r="Q140" s="7"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A141" s="6"/>
       <c r="D141" s="7"/>
       <c r="Q141" s="7"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A142" s="6"/>
       <c r="D142" s="7"/>
       <c r="Q142" s="7"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A143" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D143" s="7"/>
       <c r="Q143" s="7"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D144" s="7"/>
       <c r="Q144" s="7"/>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A145" s="6"/>
       <c r="D145" s="7"/>
       <c r="Q145" s="7"/>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A146" s="6"/>
       <c r="D146" s="7"/>
       <c r="Q146" s="7"/>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A147" s="6"/>
       <c r="D147" s="7"/>
       <c r="Q147" s="7"/>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A148" s="6"/>
       <c r="D148" s="7"/>
       <c r="Q148" s="7"/>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A149" s="6"/>
       <c r="D149" s="7"/>
       <c r="Q149" s="7"/>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A150" s="6"/>
       <c r="D150" s="7"/>
       <c r="Q150" s="7"/>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A151" s="6"/>
       <c r="D151" s="7"/>
       <c r="Q151" s="7"/>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A152" s="6"/>
       <c r="D152" s="7"/>
       <c r="Q152" s="7"/>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A153" s="8"/>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
@@ -12951,7 +16151,7 @@
       <c r="P153" s="9"/>
       <c r="Q153" s="10"/>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A157" s="1" t="s">
         <v>54</v>
       </c>
@@ -12960,7 +16160,7 @@
       <c r="D157" s="17"/>
       <c r="E157" s="14"/>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A158" s="3"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -12979,111 +16179,111 @@
       <c r="P158" s="4"/>
       <c r="Q158" s="5"/>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A159" s="6"/>
       <c r="D159" s="7"/>
       <c r="Q159" s="7"/>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A160" s="6"/>
       <c r="Q160" s="7"/>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A161" s="6"/>
       <c r="Q161" s="7"/>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A162" s="12"/>
       <c r="Q162" s="7"/>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B163" t="s">
         <v>45</v>
       </c>
       <c r="Q163" s="7"/>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A164" s="6"/>
       <c r="Q164" s="7"/>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
       <c r="C165" t="s">
         <v>46</v>
       </c>
       <c r="Q165" s="7"/>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A166" s="13"/>
       <c r="C166" t="s">
         <v>47</v>
       </c>
       <c r="Q166" s="7"/>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q167" s="7"/>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A168" s="6"/>
       <c r="Q168" s="7"/>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B169" t="s">
         <v>55</v>
       </c>
       <c r="Q169" s="7"/>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A170" s="12"/>
       <c r="Q170" s="7"/>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A171" s="6"/>
       <c r="Q171" s="7"/>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A172" s="6"/>
       <c r="Q172" s="7"/>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A173" s="13"/>
       <c r="Q173" s="7"/>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q174" s="7"/>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A175" s="6"/>
       <c r="Q175" s="7"/>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A176" s="6"/>
       <c r="Q176" s="7"/>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A177" s="6"/>
       <c r="Q177" s="7"/>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A178" s="6"/>
       <c r="Q178" s="7"/>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A179" s="6"/>
       <c r="Q179" s="7"/>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A180" s="6"/>
       <c r="Q180" s="7"/>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A181" s="6"/>
       <c r="Q181" s="7"/>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A182" s="6"/>
       <c r="Q182" s="7"/>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A183" s="8"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
@@ -13109,12 +16309,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A9F3B1-44A9-4CF1-B50E-C1EE4546BE98}">
   <dimension ref="A1:Q63"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -13140,7 +16340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -13152,19 +16352,19 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="14"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>57</v>
       </c>
@@ -13172,7 +16372,7 @@
       <c r="C8" s="17"/>
       <c r="D8" s="14"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -13191,17 +16391,17 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="D10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="D11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="D12" s="7"/>
       <c r="F12" t="s">
@@ -13209,115 +16409,115 @@
       </c>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="D15" s="7"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="7"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="D19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
       <c r="D22" s="7"/>
       <c r="Q22" s="7"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
       <c r="D23" s="7"/>
       <c r="Q23" s="7"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="7"/>
       <c r="Q24" s="7"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D25" s="7"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="6"/>
       <c r="D26" s="7"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="6"/>
       <c r="D27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="6"/>
       <c r="D28" s="7"/>
       <c r="Q28" s="7"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="6"/>
       <c r="D29" s="7"/>
       <c r="Q29" s="7"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="6"/>
       <c r="D30" s="7"/>
       <c r="Q30" s="7"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="6"/>
       <c r="D31" s="7"/>
       <c r="Q31" s="7"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="6"/>
       <c r="D32" s="7"/>
       <c r="Q32" s="7"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A33" s="6"/>
       <c r="D33" s="7"/>
       <c r="Q33" s="7"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -13336,7 +16536,7 @@
       <c r="P34" s="9"/>
       <c r="Q34" s="10"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>58</v>
       </c>
@@ -13344,7 +16544,7 @@
       <c r="C37" s="17"/>
       <c r="D37" s="14"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -13363,111 +16563,111 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="5"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A39" s="6"/>
       <c r="D39" s="7"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A40" s="6"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A41" s="6"/>
       <c r="Q41" s="7"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A42" s="12"/>
       <c r="Q42" s="7"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
         <v>39</v>
       </c>
       <c r="Q43" s="7"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A44" s="6"/>
       <c r="Q44" s="7"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q45" s="7"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A46" s="13"/>
       <c r="B46" t="s">
         <v>40</v>
       </c>
       <c r="Q46" s="7"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q47" s="7"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A48" s="6"/>
       <c r="Q48" s="7"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
         <v>41</v>
       </c>
       <c r="Q49" s="7"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A50" s="12"/>
       <c r="Q50" s="7"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A51" s="6"/>
       <c r="Q51" s="7"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A52" s="6"/>
       <c r="Q52" s="7"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A53" s="13"/>
       <c r="Q53" s="7"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q54" s="7"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A55" s="6"/>
       <c r="Q55" s="7"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A56" s="6"/>
       <c r="Q56" s="7"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A57" s="6"/>
       <c r="Q57" s="7"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A58" s="6"/>
       <c r="E58" t="s">
         <v>42</v>
       </c>
       <c r="Q58" s="7"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A59" s="6"/>
       <c r="Q59" s="7"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A60" s="6"/>
       <c r="Q60" s="7"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A61" s="6"/>
       <c r="Q61" s="7"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A62" s="6"/>
       <c r="Q62" s="7"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -13493,12 +16693,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E8C782-0759-4F82-A771-A8A9494FC1E3}">
   <dimension ref="A1:Q63"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -13524,7 +16724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>59</v>
@@ -13536,19 +16736,19 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="14"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>60</v>
       </c>
@@ -13556,7 +16756,7 @@
       <c r="C8" s="17"/>
       <c r="D8" s="14"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -13575,17 +16775,17 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="D10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="D11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="D12" s="7"/>
       <c r="F12" t="s">
@@ -13593,115 +16793,115 @@
       </c>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="D15" s="7"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="7"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="D19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
       <c r="D22" s="7"/>
       <c r="Q22" s="7"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
       <c r="D23" s="7"/>
       <c r="Q23" s="7"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="7"/>
       <c r="Q24" s="7"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D25" s="7"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="6"/>
       <c r="D26" s="7"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="6"/>
       <c r="D27" s="7"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="6"/>
       <c r="D28" s="7"/>
       <c r="Q28" s="7"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="6"/>
       <c r="D29" s="7"/>
       <c r="Q29" s="7"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="6"/>
       <c r="D30" s="7"/>
       <c r="Q30" s="7"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="6"/>
       <c r="D31" s="7"/>
       <c r="Q31" s="7"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="6"/>
       <c r="D32" s="7"/>
       <c r="Q32" s="7"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A33" s="6"/>
       <c r="D33" s="7"/>
       <c r="Q33" s="7"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -13720,7 +16920,7 @@
       <c r="P34" s="9"/>
       <c r="Q34" s="10"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>58</v>
       </c>
@@ -13728,7 +16928,7 @@
       <c r="C37" s="17"/>
       <c r="D37" s="14"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -13747,111 +16947,111 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="5"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A39" s="6"/>
       <c r="D39" s="7"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A40" s="6"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A41" s="6"/>
       <c r="Q41" s="7"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A42" s="12"/>
       <c r="Q42" s="7"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B43" t="s">
         <v>39</v>
       </c>
       <c r="Q43" s="7"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A44" s="6"/>
       <c r="Q44" s="7"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q45" s="7"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A46" s="13"/>
       <c r="B46" t="s">
         <v>40</v>
       </c>
       <c r="Q46" s="7"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q47" s="7"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A48" s="6"/>
       <c r="Q48" s="7"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
         <v>41</v>
       </c>
       <c r="Q49" s="7"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A50" s="12"/>
       <c r="Q50" s="7"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A51" s="6"/>
       <c r="Q51" s="7"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A52" s="6"/>
       <c r="Q52" s="7"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A53" s="13"/>
       <c r="Q53" s="7"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
       <c r="Q54" s="7"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A55" s="6"/>
       <c r="Q55" s="7"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A56" s="6"/>
       <c r="Q56" s="7"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A57" s="6"/>
       <c r="Q57" s="7"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A58" s="6"/>
       <c r="E58" t="s">
         <v>42</v>
       </c>
       <c r="Q58" s="7"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A59" s="6"/>
       <c r="Q59" s="7"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A60" s="6"/>
       <c r="Q60" s="7"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A61" s="6"/>
       <c r="Q61" s="7"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A62" s="6"/>
       <c r="Q62" s="7"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>

--- a/DOC/基本設計書/画面設計書.xlsx
+++ b/DOC/基本設計書/画面設計書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMap\DOC\基本設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMapDocs\DOC\03_基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558FCE52-770A-4D51-8195-74A61D0E6661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A731DE-D1E6-48A5-839E-B80DE60A1AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AD13DF4A-C6E9-46E2-8DF5-EB91E9C0FD90}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="72">
   <si>
     <t>地図機能</t>
     <rPh sb="0" eb="4">
@@ -640,12 +640,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="14">
@@ -807,7 +813,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -875,6 +881,30 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1598,7 +1628,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="2248807"/>
+          <a:off x="171450" y="2162362"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -1944,7 +1974,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="9596664"/>
+          <a:off x="171450" y="9222068"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -2334,7 +2364,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="16699593"/>
+          <a:off x="171450" y="16046450"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -2930,7 +2960,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="23802521"/>
+          <a:off x="171450" y="22870832"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -3646,8 +3676,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15519563" y="1970974"/>
-          <a:ext cx="8755607" cy="6238669"/>
+          <a:off x="15589199" y="1894133"/>
+          <a:ext cx="8797229" cy="5998543"/>
           <a:chOff x="15701689" y="1945853"/>
           <a:chExt cx="8864464" cy="6160166"/>
         </a:xfrm>
@@ -3892,7 +3922,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="2248807"/>
+          <a:off x="171450" y="2187575"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -4007,152 +4037,6 @@
         </xdr:style>
       </xdr:cxnSp>
     </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>23091</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>207819</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>34636</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>11545</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="フローチャート: 代替処理 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F11A2969-A0E7-41E2-8C97-F721EF0483A8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4925291" y="23982219"/>
-          <a:ext cx="3973945" cy="489526"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>542636</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>115454</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>57727</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>115455</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="フローチャート: 代替処理 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47DEB4CF-A440-4EA3-8C5A-537E8B9C3888}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6084454" y="4964545"/>
-          <a:ext cx="1489364" cy="461819"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>再設定</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -4252,7 +4136,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="9351736"/>
+          <a:off x="171450" y="9093200"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -4612,7 +4496,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="16454664"/>
+          <a:off x="171450" y="15998825"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -4826,7 +4710,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="23557593"/>
+          <a:off x="171450" y="22904450"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -5252,7 +5136,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="171450" y="30660521"/>
+          <a:off x="171450" y="29810075"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -5745,15 +5629,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>207818</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>11205</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>34636</xdr:colOff>
+      <xdr:colOff>1995</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>34635</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5776,188 +5660,17 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1824182"/>
-          <a:ext cx="2944091" cy="6061362"/>
+          <a:off x="1" y="1945513"/>
+          <a:ext cx="3010429" cy="6275295"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>34636</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>57725</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10AA9FFA-160E-476D-9510-BE2287604C87}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="8543636"/>
-          <a:ext cx="2944091" cy="6061362"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>34636</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>57726</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{869A38E8-8606-4FCF-8DD5-5E9A4BBF4C05}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="15240000"/>
-          <a:ext cx="2944091" cy="6061362"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>34636</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>57726</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01C8E4C1-0C92-4430-B54F-303EF5CD25D8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="21936364"/>
-          <a:ext cx="2944091" cy="6061362"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>34636</xdr:colOff>
-      <xdr:row>150</xdr:row>
-      <xdr:rowOff>57725</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4A653DD-AE71-496B-AE69-82E5FED4AAE6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="28632727"/>
-          <a:ext cx="2944091" cy="6061362"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -6059,7 +5772,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12676414" y="16454664"/>
+          <a:off x="12773025" y="15998825"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -6322,45 +6035,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3014600" cy="6425868"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="図 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6451A9A-B05D-49FF-9D2A-22796763DFE4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="9062357"/>
-          <a:ext cx="3014600" cy="6425868"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>19</xdr:col>
@@ -6458,7 +6132,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12676414" y="23557593"/>
+          <a:off x="12773025" y="22904450"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -6575,45 +6249,6 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3014600" cy="6425869"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="図 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFB45DB-A7F1-49BB-A7FE-8C22FDC027FB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="16165286"/>
-          <a:ext cx="3014600" cy="6425869"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>26</xdr:col>
@@ -6831,7 +6466,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12676414" y="9351736"/>
+          <a:off x="12773025" y="9093200"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -7094,45 +6729,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3014600" cy="6425868"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="図 75">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E97C79AC-5BD0-47B1-A4B2-DADCC4CAC144}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="9062357"/>
-          <a:ext cx="3014600" cy="6425868"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>38</xdr:col>
@@ -7230,7 +6826,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="25603200" y="16454664"/>
+          <a:off x="25803225" y="15998825"/>
           <a:ext cx="247650" cy="139700"/>
           <a:chOff x="4089400" y="3086100"/>
           <a:chExt cx="273050" cy="120650"/>
@@ -7532,6 +7128,1191 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>11545</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>41851</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="フローチャート: 代替処理 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{416AF856-6A99-4824-8D2F-6B586868D652}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5057775" y="3333750"/>
+          <a:ext cx="4126345" cy="518101"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>11545</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>41851</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="フローチャート: 代替処理 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C44C1A2A-89EC-4B5C-86F9-B2437BC22048}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5057775" y="4524375"/>
+          <a:ext cx="4126345" cy="518101"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>591127</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>106218</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>228601</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="フローチャート: 代替処理 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD5681FB-A14F-4CBA-A3AF-C49271AAE40A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6334702" y="5705475"/>
+          <a:ext cx="1572491" cy="476251"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartAlternateProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>再設定</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1994</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>233723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83EC6565-03FD-4417-A3AC-EE0154E5DA14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9062357"/>
+          <a:ext cx="2981958" cy="6356937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>260529</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>233723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FD78F20-D873-4CEB-8389-95E2C9346FDA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12504964" y="9062357"/>
+          <a:ext cx="2981958" cy="6356937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>260529</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>233723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{914A972D-7454-44CD-95C0-888E89B9AD15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12504964" y="16165286"/>
+          <a:ext cx="2981958" cy="6356937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1994</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>233723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="図 84">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EA10C92-8F31-40F8-9B9C-6026FB46DFD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="16165286"/>
+          <a:ext cx="2981958" cy="6356937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1994</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>233722</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="図 85">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E453F454-EE1A-45E2-83C1-EC17D119C40E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="23268214"/>
+          <a:ext cx="2981958" cy="6356937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>260529</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>233722</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="図 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5D44B52-98D8-474C-934C-8B9AECB0DEC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12504964" y="23268214"/>
+          <a:ext cx="2981958" cy="6356937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1994</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>233723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="図 87">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88CF38F8-8A71-4477-A201-491807DD3AAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="30371143"/>
+          <a:ext cx="2981958" cy="6356937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>449033</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>353784</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>204107</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="89" name="楕円 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC8E6609-6159-15F3-624C-B7621402EE33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4789712" y="2979964"/>
+          <a:ext cx="3986893" cy="3592286"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+            <a:alpha val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="6600"/>
+            <a:t>修正済</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>585107</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>489858</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="90" name="楕円 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F23B7E7-2514-4463-A6BC-309D416A509C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4925786" y="10450286"/>
+          <a:ext cx="3986893" cy="3592286"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+            <a:alpha val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="6600"/>
+            <a:t>未着手</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>656545</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>561296</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="91" name="楕円 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A34BC0A-D0DC-A924-8C61-3491225A99CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17491983" y="9926411"/>
+          <a:ext cx="4048126" cy="3490232"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+            <a:alpha val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="6600"/>
+            <a:t>未着手</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>37420</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>139473</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>632733</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>57830</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="92" name="楕円 91">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3959BEF0-CB87-244E-E5EB-5AD3581D8B3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5133295" y="16570098"/>
+          <a:ext cx="4048126" cy="3490232"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+            <a:alpha val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="6600"/>
+            <a:t>未着手</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>108858</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>139473</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>13609</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>57830</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="93" name="楕円 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED5E750C-D96F-5CD7-D50B-57E988CA85D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17634858" y="16331973"/>
+          <a:ext cx="4048126" cy="3490232"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+            <a:alpha val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="6600"/>
+            <a:t>未着手</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>108858</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>20411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>13609</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>176893</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="94" name="楕円 93">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89E94716-4D84-0D4F-6D14-E83AFF96F113}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5204733" y="23594786"/>
+          <a:ext cx="4048126" cy="3490232"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+            <a:alpha val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="6600"/>
+            <a:t>未着手</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>180296</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>20411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>85047</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>176893</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="95" name="楕円 94">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95ABB1BE-769D-34B0-E9E1-D6078134BC53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17706296" y="23356661"/>
+          <a:ext cx="4048126" cy="3490232"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+            <a:alpha val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="6600"/>
+            <a:t>未着手</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>418420</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>115660</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>323171</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>34017</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="96" name="楕円 95">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EA9402C-927E-9095-899A-CEC38A7BADBC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31065108" y="16784410"/>
+          <a:ext cx="4048126" cy="3490232"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+            <a:alpha val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="6600"/>
+            <a:t>未着手</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>561295</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>44224</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>466046</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>200706</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="97" name="楕円 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB9D5CD1-C827-1A21-4E5D-035B76890E56}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4966608" y="30762349"/>
+          <a:ext cx="4048126" cy="3490232"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+            <a:alpha val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="6600"/>
+            <a:t>未着手</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -13709,166 +14490,451 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="5"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="24"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="D10" s="7"/>
-      <c r="Q10" s="7"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="26"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="D11" s="7"/>
-      <c r="Q11" s="7"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="26"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="D12" s="7"/>
-      <c r="J12" t="s">
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="Q12" s="7"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="26"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="Q13" s="7"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D14" s="7"/>
-      <c r="Q14" s="7"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="26"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="D15" s="7"/>
-      <c r="I15" s="16"/>
-      <c r="Q15" s="7"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="26"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D16" s="7"/>
-      <c r="Q16" s="7"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="26"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q17" s="7"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="26"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D18" s="7"/>
-      <c r="Q18" s="7"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="26"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="D19" s="7"/>
-      <c r="Q19" s="7"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="26"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D20" s="7"/>
-      <c r="Q20" s="7"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="26"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="7"/>
-      <c r="Q21" s="7"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="26"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
       <c r="D22" s="7"/>
-      <c r="Q22" s="7"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="26"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
       <c r="D23" s="7"/>
-      <c r="Q23" s="7"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="6"/>
       <c r="D24" s="7"/>
-      <c r="Q24" s="7"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="26"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="D25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="26"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="6"/>
       <c r="D26" s="7"/>
-      <c r="Q26" s="7"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="26"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="6"/>
       <c r="D27" s="7"/>
-      <c r="Q27" s="7"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="26"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="6"/>
       <c r="D28" s="7"/>
-      <c r="Q28" s="7"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="26"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="6"/>
       <c r="D29" s="7"/>
-      <c r="Q29" s="7"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="26"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="6"/>
       <c r="D30" s="7"/>
-      <c r="Q30" s="7"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="26"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="6"/>
       <c r="D31" s="7"/>
-      <c r="Q31" s="7"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="26"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="6"/>
       <c r="D32" s="7"/>
-      <c r="Q32" s="7"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="26"/>
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A33" s="6"/>
       <c r="D33" s="7"/>
-      <c r="Q33" s="7"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="26"/>
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="10"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="29"/>
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
@@ -13891,289 +14957,856 @@
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="5"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="24"/>
       <c r="S38" s="3"/>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
       <c r="V38" s="5"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="4"/>
-      <c r="AC38" s="4"/>
-      <c r="AD38" s="4"/>
-      <c r="AE38" s="4"/>
-      <c r="AF38" s="4"/>
-      <c r="AG38" s="4"/>
-      <c r="AH38" s="4"/>
-      <c r="AI38" s="5"/>
+      <c r="W38" s="23"/>
+      <c r="X38" s="23"/>
+      <c r="Y38" s="23"/>
+      <c r="Z38" s="23"/>
+      <c r="AA38" s="23"/>
+      <c r="AB38" s="23"/>
+      <c r="AC38" s="23"/>
+      <c r="AD38" s="23"/>
+      <c r="AE38" s="23"/>
+      <c r="AF38" s="23"/>
+      <c r="AG38" s="23"/>
+      <c r="AH38" s="23"/>
+      <c r="AI38" s="24"/>
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A39" s="6"/>
       <c r="D39" s="7"/>
-      <c r="Q39" s="7"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="26"/>
       <c r="S39" s="6"/>
       <c r="V39" s="7"/>
-      <c r="AI39" s="7"/>
+      <c r="W39" s="25"/>
+      <c r="X39" s="25"/>
+      <c r="Y39" s="25"/>
+      <c r="Z39" s="25"/>
+      <c r="AA39" s="25"/>
+      <c r="AB39" s="25"/>
+      <c r="AC39" s="25"/>
+      <c r="AD39" s="25"/>
+      <c r="AE39" s="25"/>
+      <c r="AF39" s="25"/>
+      <c r="AG39" s="25"/>
+      <c r="AH39" s="25"/>
+      <c r="AI39" s="26"/>
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A40" s="6"/>
       <c r="D40" s="7"/>
-      <c r="Q40" s="7"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="25"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="25"/>
+      <c r="P40" s="25"/>
+      <c r="Q40" s="26"/>
       <c r="S40" s="6"/>
       <c r="V40" s="7"/>
-      <c r="AI40" s="7"/>
+      <c r="W40" s="25"/>
+      <c r="X40" s="25"/>
+      <c r="Y40" s="25"/>
+      <c r="Z40" s="25"/>
+      <c r="AA40" s="25"/>
+      <c r="AB40" s="25"/>
+      <c r="AC40" s="25"/>
+      <c r="AD40" s="25"/>
+      <c r="AE40" s="25"/>
+      <c r="AF40" s="25"/>
+      <c r="AG40" s="25"/>
+      <c r="AH40" s="25"/>
+      <c r="AI40" s="26"/>
     </row>
     <row r="41" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A41" s="6"/>
       <c r="D41" s="7"/>
-      <c r="J41" t="s">
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="Q41" s="7"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+      <c r="M41" s="25"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="25"/>
+      <c r="P41" s="25"/>
+      <c r="Q41" s="26"/>
       <c r="S41" s="6"/>
       <c r="V41" s="7"/>
-      <c r="AB41" t="s">
+      <c r="W41" s="25"/>
+      <c r="X41" s="25"/>
+      <c r="Y41" s="25"/>
+      <c r="Z41" s="25"/>
+      <c r="AA41" s="25"/>
+      <c r="AB41" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="AI41" s="7"/>
+      <c r="AC41" s="25"/>
+      <c r="AD41" s="25"/>
+      <c r="AE41" s="25"/>
+      <c r="AF41" s="25"/>
+      <c r="AG41" s="25"/>
+      <c r="AH41" s="25"/>
+      <c r="AI41" s="26"/>
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A42" s="12" t="s">
         <v>14</v>
       </c>
       <c r="D42" s="7"/>
-      <c r="Q42" s="7"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="25"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="25"/>
+      <c r="P42" s="25"/>
+      <c r="Q42" s="26"/>
       <c r="S42" s="12" t="s">
         <v>14</v>
       </c>
       <c r="V42" s="7"/>
-      <c r="AI42" s="7"/>
+      <c r="W42" s="25"/>
+      <c r="X42" s="25"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="25"/>
+      <c r="AA42" s="25"/>
+      <c r="AB42" s="25"/>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="25"/>
+      <c r="AE42" s="25"/>
+      <c r="AF42" s="25"/>
+      <c r="AG42" s="25"/>
+      <c r="AH42" s="25"/>
+      <c r="AI42" s="26"/>
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D43" s="7"/>
-      <c r="Q43" s="7"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="25"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="25"/>
+      <c r="L43" s="25"/>
+      <c r="M43" s="25"/>
+      <c r="N43" s="25"/>
+      <c r="O43" s="25"/>
+      <c r="P43" s="25"/>
+      <c r="Q43" s="26"/>
       <c r="V43" s="7"/>
-      <c r="AI43" s="7"/>
+      <c r="W43" s="25"/>
+      <c r="X43" s="25"/>
+      <c r="Y43" s="25"/>
+      <c r="Z43" s="25"/>
+      <c r="AA43" s="25"/>
+      <c r="AB43" s="25"/>
+      <c r="AC43" s="25"/>
+      <c r="AD43" s="25"/>
+      <c r="AE43" s="25"/>
+      <c r="AF43" s="25"/>
+      <c r="AG43" s="25"/>
+      <c r="AH43" s="25"/>
+      <c r="AI43" s="26"/>
     </row>
     <row r="44" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A44" s="6"/>
       <c r="D44" s="7"/>
-      <c r="I44" s="16"/>
-      <c r="Q44" s="7"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="25"/>
+      <c r="N44" s="25"/>
+      <c r="O44" s="25"/>
+      <c r="P44" s="25"/>
+      <c r="Q44" s="26"/>
       <c r="S44" s="6"/>
       <c r="V44" s="7"/>
-      <c r="Z44" s="16" t="s">
+      <c r="W44" s="25"/>
+      <c r="X44" s="25"/>
+      <c r="Y44" s="25"/>
+      <c r="Z44" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="AA44" s="16"/>
-      <c r="AI44" s="7"/>
+      <c r="AA44" s="27"/>
+      <c r="AB44" s="25"/>
+      <c r="AC44" s="25"/>
+      <c r="AD44" s="25"/>
+      <c r="AE44" s="25"/>
+      <c r="AF44" s="25"/>
+      <c r="AG44" s="25"/>
+      <c r="AH44" s="25"/>
+      <c r="AI44" s="26"/>
     </row>
     <row r="45" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D45" s="7"/>
-      <c r="Q45" s="7"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="25"/>
+      <c r="M45" s="25"/>
+      <c r="N45" s="25"/>
+      <c r="O45" s="25"/>
+      <c r="P45" s="25"/>
+      <c r="Q45" s="26"/>
       <c r="V45" s="7"/>
-      <c r="AI45" s="7"/>
+      <c r="W45" s="25"/>
+      <c r="X45" s="25"/>
+      <c r="Y45" s="25"/>
+      <c r="Z45" s="25"/>
+      <c r="AA45" s="25"/>
+      <c r="AB45" s="25"/>
+      <c r="AC45" s="25"/>
+      <c r="AD45" s="25"/>
+      <c r="AE45" s="25"/>
+      <c r="AF45" s="25"/>
+      <c r="AG45" s="25"/>
+      <c r="AH45" s="25"/>
+      <c r="AI45" s="26"/>
     </row>
     <row r="46" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A46" s="13" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="7"/>
-      <c r="H46" t="s">
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="Q46" s="7"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="25"/>
+      <c r="M46" s="25"/>
+      <c r="N46" s="25"/>
+      <c r="O46" s="25"/>
+      <c r="P46" s="25"/>
+      <c r="Q46" s="26"/>
       <c r="S46" s="13" t="s">
         <v>15</v>
       </c>
       <c r="V46" s="7"/>
-      <c r="Z46" t="s">
+      <c r="W46" s="25"/>
+      <c r="X46" s="25"/>
+      <c r="Y46" s="25"/>
+      <c r="Z46" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="AI46" s="7"/>
+      <c r="AA46" s="25"/>
+      <c r="AB46" s="25"/>
+      <c r="AC46" s="25"/>
+      <c r="AD46" s="25"/>
+      <c r="AE46" s="25"/>
+      <c r="AF46" s="25"/>
+      <c r="AG46" s="25"/>
+      <c r="AH46" s="25"/>
+      <c r="AI46" s="26"/>
     </row>
     <row r="47" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D47" s="7"/>
-      <c r="Q47" s="7"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="25"/>
+      <c r="M47" s="25"/>
+      <c r="N47" s="25"/>
+      <c r="O47" s="25"/>
+      <c r="P47" s="25"/>
+      <c r="Q47" s="26"/>
       <c r="V47" s="7"/>
-      <c r="AI47" s="7"/>
+      <c r="W47" s="25"/>
+      <c r="X47" s="25"/>
+      <c r="Y47" s="25"/>
+      <c r="Z47" s="25"/>
+      <c r="AA47" s="25"/>
+      <c r="AB47" s="25"/>
+      <c r="AC47" s="25"/>
+      <c r="AD47" s="25"/>
+      <c r="AE47" s="25"/>
+      <c r="AF47" s="25"/>
+      <c r="AG47" s="25"/>
+      <c r="AH47" s="25"/>
+      <c r="AI47" s="26"/>
     </row>
     <row r="48" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A48" s="6"/>
       <c r="D48" s="7"/>
-      <c r="Q48" s="7"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="25"/>
+      <c r="L48" s="25"/>
+      <c r="M48" s="25"/>
+      <c r="N48" s="25"/>
+      <c r="O48" s="25"/>
+      <c r="P48" s="25"/>
+      <c r="Q48" s="26"/>
       <c r="S48" s="6"/>
       <c r="V48" s="7"/>
-      <c r="AI48" s="7"/>
+      <c r="W48" s="25"/>
+      <c r="X48" s="25"/>
+      <c r="Y48" s="25"/>
+      <c r="Z48" s="25"/>
+      <c r="AA48" s="25"/>
+      <c r="AB48" s="25"/>
+      <c r="AC48" s="25"/>
+      <c r="AD48" s="25"/>
+      <c r="AE48" s="25"/>
+      <c r="AF48" s="25"/>
+      <c r="AG48" s="25"/>
+      <c r="AH48" s="25"/>
+      <c r="AI48" s="26"/>
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D49" s="7"/>
-      <c r="Q49" s="7"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="25"/>
+      <c r="I49" s="25"/>
+      <c r="J49" s="25"/>
+      <c r="K49" s="25"/>
+      <c r="L49" s="25"/>
+      <c r="M49" s="25"/>
+      <c r="N49" s="25"/>
+      <c r="O49" s="25"/>
+      <c r="P49" s="25"/>
+      <c r="Q49" s="26"/>
       <c r="V49" s="7"/>
-      <c r="AI49" s="7"/>
+      <c r="W49" s="25"/>
+      <c r="X49" s="25"/>
+      <c r="Y49" s="25"/>
+      <c r="Z49" s="25"/>
+      <c r="AA49" s="25"/>
+      <c r="AB49" s="25"/>
+      <c r="AC49" s="25"/>
+      <c r="AD49" s="25"/>
+      <c r="AE49" s="25"/>
+      <c r="AF49" s="25"/>
+      <c r="AG49" s="25"/>
+      <c r="AH49" s="25"/>
+      <c r="AI49" s="26"/>
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A50" s="12" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="7"/>
-      <c r="Q50" s="7"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25"/>
+      <c r="N50" s="25"/>
+      <c r="O50" s="25"/>
+      <c r="P50" s="25"/>
+      <c r="Q50" s="26"/>
       <c r="S50" s="12" t="s">
         <v>13</v>
       </c>
       <c r="V50" s="7"/>
-      <c r="AI50" s="7"/>
+      <c r="W50" s="25"/>
+      <c r="X50" s="25"/>
+      <c r="Y50" s="25"/>
+      <c r="Z50" s="25"/>
+      <c r="AA50" s="25"/>
+      <c r="AB50" s="25"/>
+      <c r="AC50" s="25"/>
+      <c r="AD50" s="25"/>
+      <c r="AE50" s="25"/>
+      <c r="AF50" s="25"/>
+      <c r="AG50" s="25"/>
+      <c r="AH50" s="25"/>
+      <c r="AI50" s="26"/>
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A51" s="6"/>
       <c r="D51" s="7"/>
-      <c r="Q51" s="7"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="25"/>
+      <c r="L51" s="25"/>
+      <c r="M51" s="25"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="25"/>
+      <c r="P51" s="25"/>
+      <c r="Q51" s="26"/>
       <c r="S51" s="6"/>
       <c r="V51" s="7"/>
-      <c r="AI51" s="7"/>
+      <c r="W51" s="25"/>
+      <c r="X51" s="25"/>
+      <c r="Y51" s="25"/>
+      <c r="Z51" s="25"/>
+      <c r="AA51" s="25"/>
+      <c r="AB51" s="25"/>
+      <c r="AC51" s="25"/>
+      <c r="AD51" s="25"/>
+      <c r="AE51" s="25"/>
+      <c r="AF51" s="25"/>
+      <c r="AG51" s="25"/>
+      <c r="AH51" s="25"/>
+      <c r="AI51" s="26"/>
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A52" s="6"/>
       <c r="D52" s="7"/>
-      <c r="Q52" s="7"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="25"/>
+      <c r="J52" s="25"/>
+      <c r="K52" s="25"/>
+      <c r="L52" s="25"/>
+      <c r="M52" s="25"/>
+      <c r="N52" s="25"/>
+      <c r="O52" s="25"/>
+      <c r="P52" s="25"/>
+      <c r="Q52" s="26"/>
       <c r="S52" s="6"/>
       <c r="V52" s="7"/>
-      <c r="AI52" s="7"/>
+      <c r="W52" s="25"/>
+      <c r="X52" s="25"/>
+      <c r="Y52" s="25"/>
+      <c r="Z52" s="25"/>
+      <c r="AA52" s="25"/>
+      <c r="AB52" s="25"/>
+      <c r="AC52" s="25"/>
+      <c r="AD52" s="25"/>
+      <c r="AE52" s="25"/>
+      <c r="AF52" s="25"/>
+      <c r="AG52" s="25"/>
+      <c r="AH52" s="25"/>
+      <c r="AI52" s="26"/>
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A53" s="6"/>
       <c r="D53" s="7"/>
-      <c r="Q53" s="7"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="25"/>
+      <c r="N53" s="25"/>
+      <c r="O53" s="25"/>
+      <c r="P53" s="25"/>
+      <c r="Q53" s="26"/>
       <c r="S53" s="6"/>
       <c r="V53" s="7"/>
-      <c r="AI53" s="7"/>
+      <c r="W53" s="25"/>
+      <c r="X53" s="25"/>
+      <c r="Y53" s="25"/>
+      <c r="Z53" s="25"/>
+      <c r="AA53" s="25"/>
+      <c r="AB53" s="25"/>
+      <c r="AC53" s="25"/>
+      <c r="AD53" s="25"/>
+      <c r="AE53" s="25"/>
+      <c r="AF53" s="25"/>
+      <c r="AG53" s="25"/>
+      <c r="AH53" s="25"/>
+      <c r="AI53" s="26"/>
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.4">
       <c r="D54" s="7"/>
-      <c r="Q54" s="7"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="25"/>
+      <c r="M54" s="25"/>
+      <c r="N54" s="25"/>
+      <c r="O54" s="25"/>
+      <c r="P54" s="25"/>
+      <c r="Q54" s="26"/>
       <c r="V54" s="7"/>
-      <c r="AI54" s="7"/>
+      <c r="W54" s="25"/>
+      <c r="X54" s="25"/>
+      <c r="Y54" s="25"/>
+      <c r="Z54" s="25"/>
+      <c r="AA54" s="25"/>
+      <c r="AB54" s="25"/>
+      <c r="AC54" s="25"/>
+      <c r="AD54" s="25"/>
+      <c r="AE54" s="25"/>
+      <c r="AF54" s="25"/>
+      <c r="AG54" s="25"/>
+      <c r="AH54" s="25"/>
+      <c r="AI54" s="26"/>
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A55" s="6"/>
       <c r="D55" s="7"/>
-      <c r="I55" s="11" t="s">
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="Q55" s="7"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="25"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="25"/>
+      <c r="P55" s="25"/>
+      <c r="Q55" s="26"/>
       <c r="S55" s="6"/>
       <c r="V55" s="7"/>
-      <c r="AA55" s="11" t="s">
+      <c r="W55" s="25"/>
+      <c r="X55" s="25"/>
+      <c r="Y55" s="25"/>
+      <c r="Z55" s="25"/>
+      <c r="AA55" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="AI55" s="7"/>
+      <c r="AB55" s="25"/>
+      <c r="AC55" s="25"/>
+      <c r="AD55" s="25"/>
+      <c r="AE55" s="25"/>
+      <c r="AF55" s="25"/>
+      <c r="AG55" s="25"/>
+      <c r="AH55" s="25"/>
+      <c r="AI55" s="26"/>
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A56" s="6"/>
       <c r="D56" s="7"/>
-      <c r="Q56" s="7"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="25"/>
+      <c r="M56" s="25"/>
+      <c r="N56" s="25"/>
+      <c r="O56" s="25"/>
+      <c r="P56" s="25"/>
+      <c r="Q56" s="26"/>
       <c r="S56" s="6"/>
       <c r="V56" s="7"/>
-      <c r="AI56" s="7"/>
+      <c r="W56" s="25"/>
+      <c r="X56" s="25"/>
+      <c r="Y56" s="25"/>
+      <c r="Z56" s="25"/>
+      <c r="AA56" s="25"/>
+      <c r="AB56" s="25"/>
+      <c r="AC56" s="25"/>
+      <c r="AD56" s="25"/>
+      <c r="AE56" s="25"/>
+      <c r="AF56" s="25"/>
+      <c r="AG56" s="25"/>
+      <c r="AH56" s="25"/>
+      <c r="AI56" s="26"/>
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A57" s="6"/>
       <c r="D57" s="7"/>
-      <c r="Q57" s="7"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="25"/>
+      <c r="L57" s="25"/>
+      <c r="M57" s="25"/>
+      <c r="N57" s="25"/>
+      <c r="O57" s="25"/>
+      <c r="P57" s="25"/>
+      <c r="Q57" s="26"/>
       <c r="S57" s="6"/>
       <c r="V57" s="7"/>
-      <c r="AI57" s="7"/>
+      <c r="W57" s="25"/>
+      <c r="X57" s="25"/>
+      <c r="Y57" s="25"/>
+      <c r="Z57" s="25"/>
+      <c r="AA57" s="25"/>
+      <c r="AB57" s="25"/>
+      <c r="AC57" s="25"/>
+      <c r="AD57" s="25"/>
+      <c r="AE57" s="25"/>
+      <c r="AF57" s="25"/>
+      <c r="AG57" s="25"/>
+      <c r="AH57" s="25"/>
+      <c r="AI57" s="26"/>
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A58" s="6"/>
       <c r="D58" s="7"/>
-      <c r="Q58" s="7"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="25"/>
+      <c r="M58" s="25"/>
+      <c r="N58" s="25"/>
+      <c r="O58" s="25"/>
+      <c r="P58" s="25"/>
+      <c r="Q58" s="26"/>
       <c r="S58" s="6"/>
       <c r="V58" s="7"/>
-      <c r="AI58" s="7"/>
+      <c r="W58" s="25"/>
+      <c r="X58" s="25"/>
+      <c r="Y58" s="25"/>
+      <c r="Z58" s="25"/>
+      <c r="AA58" s="25"/>
+      <c r="AB58" s="25"/>
+      <c r="AC58" s="25"/>
+      <c r="AD58" s="25"/>
+      <c r="AE58" s="25"/>
+      <c r="AF58" s="25"/>
+      <c r="AG58" s="25"/>
+      <c r="AH58" s="25"/>
+      <c r="AI58" s="26"/>
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A59" s="6"/>
       <c r="D59" s="7"/>
-      <c r="Q59" s="7"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="25"/>
+      <c r="L59" s="25"/>
+      <c r="M59" s="25"/>
+      <c r="N59" s="25"/>
+      <c r="O59" s="25"/>
+      <c r="P59" s="25"/>
+      <c r="Q59" s="26"/>
       <c r="S59" s="6"/>
       <c r="V59" s="7"/>
-      <c r="AI59" s="7"/>
+      <c r="W59" s="25"/>
+      <c r="X59" s="25"/>
+      <c r="Y59" s="25"/>
+      <c r="Z59" s="25"/>
+      <c r="AA59" s="25"/>
+      <c r="AB59" s="25"/>
+      <c r="AC59" s="25"/>
+      <c r="AD59" s="25"/>
+      <c r="AE59" s="25"/>
+      <c r="AF59" s="25"/>
+      <c r="AG59" s="25"/>
+      <c r="AH59" s="25"/>
+      <c r="AI59" s="26"/>
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A60" s="6"/>
       <c r="D60" s="7"/>
-      <c r="Q60" s="7"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="25"/>
+      <c r="L60" s="25"/>
+      <c r="M60" s="25"/>
+      <c r="N60" s="25"/>
+      <c r="O60" s="25"/>
+      <c r="P60" s="25"/>
+      <c r="Q60" s="26"/>
       <c r="S60" s="6"/>
       <c r="V60" s="7"/>
-      <c r="AI60" s="7"/>
+      <c r="W60" s="25"/>
+      <c r="X60" s="25"/>
+      <c r="Y60" s="25"/>
+      <c r="Z60" s="25"/>
+      <c r="AA60" s="25"/>
+      <c r="AB60" s="25"/>
+      <c r="AC60" s="25"/>
+      <c r="AD60" s="25"/>
+      <c r="AE60" s="25"/>
+      <c r="AF60" s="25"/>
+      <c r="AG60" s="25"/>
+      <c r="AH60" s="25"/>
+      <c r="AI60" s="26"/>
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A61" s="6"/>
       <c r="D61" s="7"/>
-      <c r="Q61" s="7"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="25"/>
+      <c r="P61" s="25"/>
+      <c r="Q61" s="26"/>
       <c r="S61" s="6"/>
       <c r="V61" s="7"/>
-      <c r="AI61" s="7"/>
+      <c r="W61" s="25"/>
+      <c r="X61" s="25"/>
+      <c r="Y61" s="25"/>
+      <c r="Z61" s="25"/>
+      <c r="AA61" s="25"/>
+      <c r="AB61" s="25"/>
+      <c r="AC61" s="25"/>
+      <c r="AD61" s="25"/>
+      <c r="AE61" s="25"/>
+      <c r="AF61" s="25"/>
+      <c r="AG61" s="25"/>
+      <c r="AH61" s="25"/>
+      <c r="AI61" s="26"/>
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A62" s="6"/>
       <c r="D62" s="7"/>
-      <c r="Q62" s="7"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="25"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="25"/>
+      <c r="L62" s="25"/>
+      <c r="M62" s="25"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="25"/>
+      <c r="P62" s="25"/>
+      <c r="Q62" s="26"/>
       <c r="S62" s="6"/>
       <c r="V62" s="7"/>
-      <c r="AI62" s="7"/>
+      <c r="W62" s="25"/>
+      <c r="X62" s="25"/>
+      <c r="Y62" s="25"/>
+      <c r="Z62" s="25"/>
+      <c r="AA62" s="25"/>
+      <c r="AB62" s="25"/>
+      <c r="AC62" s="25"/>
+      <c r="AD62" s="25"/>
+      <c r="AE62" s="25"/>
+      <c r="AF62" s="25"/>
+      <c r="AG62" s="25"/>
+      <c r="AH62" s="25"/>
+      <c r="AI62" s="26"/>
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
       <c r="D63" s="10"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="9"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
-      <c r="M63" s="9"/>
-      <c r="N63" s="9"/>
-      <c r="O63" s="9"/>
-      <c r="P63" s="9"/>
-      <c r="Q63" s="10"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="28"/>
+      <c r="K63" s="28"/>
+      <c r="L63" s="28"/>
+      <c r="M63" s="28"/>
+      <c r="N63" s="28"/>
+      <c r="O63" s="28"/>
+      <c r="P63" s="28"/>
+      <c r="Q63" s="29"/>
       <c r="S63" s="8"/>
       <c r="T63" s="9"/>
       <c r="U63" s="9"/>
       <c r="V63" s="10"/>
-      <c r="W63" s="9"/>
-      <c r="X63" s="9"/>
-      <c r="Y63" s="9"/>
-      <c r="Z63" s="9"/>
-      <c r="AA63" s="9"/>
-      <c r="AB63" s="9"/>
-      <c r="AC63" s="9"/>
-      <c r="AD63" s="9"/>
-      <c r="AE63" s="9"/>
-      <c r="AF63" s="9"/>
-      <c r="AG63" s="9"/>
-      <c r="AH63" s="9"/>
-      <c r="AI63" s="10"/>
+      <c r="W63" s="28"/>
+      <c r="X63" s="28"/>
+      <c r="Y63" s="28"/>
+      <c r="Z63" s="28"/>
+      <c r="AA63" s="28"/>
+      <c r="AB63" s="28"/>
+      <c r="AC63" s="28"/>
+      <c r="AD63" s="28"/>
+      <c r="AE63" s="28"/>
+      <c r="AF63" s="28"/>
+      <c r="AG63" s="28"/>
+      <c r="AH63" s="28"/>
+      <c r="AI63" s="29"/>
     </row>
     <row r="66" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
@@ -14202,36 +15835,36 @@
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="5"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="5"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
+      <c r="I67" s="23"/>
+      <c r="J67" s="23"/>
+      <c r="K67" s="23"/>
+      <c r="L67" s="23"/>
+      <c r="M67" s="23"/>
+      <c r="N67" s="23"/>
+      <c r="O67" s="23"/>
+      <c r="P67" s="23"/>
+      <c r="Q67" s="24"/>
       <c r="S67" s="3"/>
       <c r="T67" s="4"/>
       <c r="U67" s="4"/>
       <c r="V67" s="5"/>
-      <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
-      <c r="Y67" s="4"/>
-      <c r="Z67" s="4"/>
-      <c r="AA67" s="4"/>
-      <c r="AB67" s="4"/>
-      <c r="AC67" s="4"/>
-      <c r="AD67" s="4"/>
-      <c r="AE67" s="4"/>
-      <c r="AF67" s="4"/>
-      <c r="AG67" s="4"/>
-      <c r="AH67" s="4"/>
-      <c r="AI67" s="5"/>
+      <c r="W67" s="23"/>
+      <c r="X67" s="23"/>
+      <c r="Y67" s="23"/>
+      <c r="Z67" s="23"/>
+      <c r="AA67" s="23"/>
+      <c r="AB67" s="23"/>
+      <c r="AC67" s="23"/>
+      <c r="AD67" s="23"/>
+      <c r="AE67" s="23"/>
+      <c r="AF67" s="23"/>
+      <c r="AG67" s="23"/>
+      <c r="AH67" s="23"/>
+      <c r="AI67" s="24"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="4"/>
       <c r="AN67" s="4"/>
@@ -14253,10 +15886,34 @@
     <row r="68" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A68" s="6"/>
       <c r="D68" s="7"/>
-      <c r="Q68" s="7"/>
+      <c r="E68" s="25"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25"/>
+      <c r="J68" s="25"/>
+      <c r="K68" s="25"/>
+      <c r="L68" s="25"/>
+      <c r="M68" s="25"/>
+      <c r="N68" s="25"/>
+      <c r="O68" s="25"/>
+      <c r="P68" s="25"/>
+      <c r="Q68" s="26"/>
       <c r="S68" s="6"/>
       <c r="V68" s="7"/>
-      <c r="AI68" s="7"/>
+      <c r="W68" s="25"/>
+      <c r="X68" s="25"/>
+      <c r="Y68" s="25"/>
+      <c r="Z68" s="25"/>
+      <c r="AA68" s="25"/>
+      <c r="AB68" s="25"/>
+      <c r="AC68" s="25"/>
+      <c r="AD68" s="25"/>
+      <c r="AE68" s="25"/>
+      <c r="AF68" s="25"/>
+      <c r="AG68" s="25"/>
+      <c r="AH68" s="25"/>
+      <c r="AI68" s="26"/>
       <c r="AL68" s="6"/>
       <c r="AO68" s="7"/>
       <c r="BB68" s="7"/>
@@ -14264,10 +15921,34 @@
     <row r="69" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A69" s="6"/>
       <c r="D69" s="7"/>
-      <c r="Q69" s="7"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="25"/>
+      <c r="K69" s="25"/>
+      <c r="L69" s="25"/>
+      <c r="M69" s="25"/>
+      <c r="N69" s="25"/>
+      <c r="O69" s="25"/>
+      <c r="P69" s="25"/>
+      <c r="Q69" s="26"/>
       <c r="S69" s="6"/>
       <c r="V69" s="7"/>
-      <c r="AI69" s="7"/>
+      <c r="W69" s="25"/>
+      <c r="X69" s="25"/>
+      <c r="Y69" s="25"/>
+      <c r="Z69" s="25"/>
+      <c r="AA69" s="25"/>
+      <c r="AB69" s="25"/>
+      <c r="AC69" s="25"/>
+      <c r="AD69" s="25"/>
+      <c r="AE69" s="25"/>
+      <c r="AF69" s="25"/>
+      <c r="AG69" s="25"/>
+      <c r="AH69" s="25"/>
+      <c r="AI69" s="26"/>
       <c r="AL69" s="6"/>
       <c r="AO69" s="7"/>
       <c r="BB69" s="7"/>
@@ -14275,16 +15956,38 @@
     <row r="70" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A70" s="6"/>
       <c r="D70" s="7"/>
-      <c r="J70" t="s">
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="25"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="Q70" s="7"/>
+      <c r="K70" s="25"/>
+      <c r="L70" s="25"/>
+      <c r="M70" s="25"/>
+      <c r="N70" s="25"/>
+      <c r="O70" s="25"/>
+      <c r="P70" s="25"/>
+      <c r="Q70" s="26"/>
       <c r="S70" s="6"/>
       <c r="V70" s="7"/>
-      <c r="AB70" t="s">
+      <c r="W70" s="25"/>
+      <c r="X70" s="25"/>
+      <c r="Y70" s="25"/>
+      <c r="Z70" s="25"/>
+      <c r="AA70" s="25"/>
+      <c r="AB70" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="AI70" s="7"/>
+      <c r="AC70" s="25"/>
+      <c r="AD70" s="25"/>
+      <c r="AE70" s="25"/>
+      <c r="AF70" s="25"/>
+      <c r="AG70" s="25"/>
+      <c r="AH70" s="25"/>
+      <c r="AI70" s="26"/>
       <c r="AL70" s="6"/>
       <c r="AO70" s="7"/>
       <c r="AU70" t="s">
@@ -14297,12 +16000,36 @@
         <v>14</v>
       </c>
       <c r="D71" s="7"/>
-      <c r="Q71" s="7"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
+      <c r="H71" s="25"/>
+      <c r="I71" s="25"/>
+      <c r="J71" s="25"/>
+      <c r="K71" s="25"/>
+      <c r="L71" s="25"/>
+      <c r="M71" s="25"/>
+      <c r="N71" s="25"/>
+      <c r="O71" s="25"/>
+      <c r="P71" s="25"/>
+      <c r="Q71" s="26"/>
       <c r="S71" s="12" t="s">
         <v>14</v>
       </c>
       <c r="V71" s="7"/>
-      <c r="AI71" s="7"/>
+      <c r="W71" s="25"/>
+      <c r="X71" s="25"/>
+      <c r="Y71" s="25"/>
+      <c r="Z71" s="25"/>
+      <c r="AA71" s="25"/>
+      <c r="AB71" s="25"/>
+      <c r="AC71" s="25"/>
+      <c r="AD71" s="25"/>
+      <c r="AE71" s="25"/>
+      <c r="AF71" s="25"/>
+      <c r="AG71" s="25"/>
+      <c r="AH71" s="25"/>
+      <c r="AI71" s="26"/>
       <c r="AL71" s="12" t="s">
         <v>14</v>
       </c>
@@ -14311,21 +16038,67 @@
     </row>
     <row r="72" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D72" s="7"/>
-      <c r="Q72" s="7"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25"/>
+      <c r="I72" s="25"/>
+      <c r="J72" s="25"/>
+      <c r="K72" s="25"/>
+      <c r="L72" s="25"/>
+      <c r="M72" s="25"/>
+      <c r="N72" s="25"/>
+      <c r="O72" s="25"/>
+      <c r="P72" s="25"/>
+      <c r="Q72" s="26"/>
       <c r="V72" s="7"/>
-      <c r="AI72" s="7"/>
+      <c r="W72" s="25"/>
+      <c r="X72" s="25"/>
+      <c r="Y72" s="25"/>
+      <c r="Z72" s="25"/>
+      <c r="AA72" s="25"/>
+      <c r="AB72" s="25"/>
+      <c r="AC72" s="25"/>
+      <c r="AD72" s="25"/>
+      <c r="AE72" s="25"/>
+      <c r="AF72" s="25"/>
+      <c r="AG72" s="25"/>
+      <c r="AH72" s="25"/>
+      <c r="AI72" s="26"/>
       <c r="AO72" s="7"/>
       <c r="BB72" s="7"/>
     </row>
     <row r="73" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A73" s="6"/>
       <c r="D73" s="7"/>
-      <c r="I73" s="16"/>
-      <c r="Q73" s="7"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="27"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="25"/>
+      <c r="L73" s="25"/>
+      <c r="M73" s="25"/>
+      <c r="N73" s="25"/>
+      <c r="O73" s="25"/>
+      <c r="P73" s="25"/>
+      <c r="Q73" s="26"/>
       <c r="S73" s="6"/>
       <c r="V73" s="7"/>
-      <c r="AA73" s="16"/>
-      <c r="AI73" s="7"/>
+      <c r="W73" s="25"/>
+      <c r="X73" s="25"/>
+      <c r="Y73" s="25"/>
+      <c r="Z73" s="25"/>
+      <c r="AA73" s="27"/>
+      <c r="AB73" s="25"/>
+      <c r="AC73" s="25"/>
+      <c r="AD73" s="25"/>
+      <c r="AE73" s="25"/>
+      <c r="AF73" s="25"/>
+      <c r="AG73" s="25"/>
+      <c r="AH73" s="25"/>
+      <c r="AI73" s="26"/>
       <c r="AL73" s="6"/>
       <c r="AO73" s="7"/>
       <c r="AS73" s="16" t="s">
@@ -14336,9 +16109,33 @@
     </row>
     <row r="74" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D74" s="7"/>
-      <c r="Q74" s="7"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25"/>
+      <c r="I74" s="25"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="25"/>
+      <c r="L74" s="25"/>
+      <c r="M74" s="25"/>
+      <c r="N74" s="25"/>
+      <c r="O74" s="25"/>
+      <c r="P74" s="25"/>
+      <c r="Q74" s="26"/>
       <c r="V74" s="7"/>
-      <c r="AI74" s="7"/>
+      <c r="W74" s="25"/>
+      <c r="X74" s="25"/>
+      <c r="Y74" s="25"/>
+      <c r="Z74" s="25"/>
+      <c r="AA74" s="25"/>
+      <c r="AB74" s="25"/>
+      <c r="AC74" s="25"/>
+      <c r="AD74" s="25"/>
+      <c r="AE74" s="25"/>
+      <c r="AF74" s="25"/>
+      <c r="AG74" s="25"/>
+      <c r="AH74" s="25"/>
+      <c r="AI74" s="26"/>
       <c r="AO74" s="7"/>
       <c r="BB74" s="7"/>
     </row>
@@ -14347,15 +16144,38 @@
         <v>15</v>
       </c>
       <c r="D75" s="7"/>
-      <c r="Q75" s="7"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25"/>
+      <c r="I75" s="25"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="25"/>
+      <c r="L75" s="25"/>
+      <c r="M75" s="25"/>
+      <c r="N75" s="25"/>
+      <c r="O75" s="25"/>
+      <c r="P75" s="25"/>
+      <c r="Q75" s="26"/>
       <c r="S75" s="13" t="s">
         <v>15</v>
       </c>
       <c r="V75" s="7"/>
-      <c r="Z75" t="s">
+      <c r="W75" s="25"/>
+      <c r="X75" s="25"/>
+      <c r="Y75" s="25"/>
+      <c r="Z75" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="AI75" s="7"/>
+      <c r="AA75" s="25"/>
+      <c r="AB75" s="25"/>
+      <c r="AC75" s="25"/>
+      <c r="AD75" s="25"/>
+      <c r="AE75" s="25"/>
+      <c r="AF75" s="25"/>
+      <c r="AG75" s="25"/>
+      <c r="AH75" s="25"/>
+      <c r="AI75" s="26"/>
       <c r="AL75" s="13" t="s">
         <v>15</v>
       </c>
@@ -14367,31 +16187,102 @@
     </row>
     <row r="76" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D76" s="7"/>
-      <c r="H76" t="s">
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="Q76" s="7"/>
+      <c r="I76" s="25"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="25"/>
+      <c r="L76" s="25"/>
+      <c r="M76" s="25"/>
+      <c r="N76" s="25"/>
+      <c r="O76" s="25"/>
+      <c r="P76" s="25"/>
+      <c r="Q76" s="26"/>
       <c r="V76" s="7"/>
-      <c r="AI76" s="7"/>
+      <c r="W76" s="25"/>
+      <c r="X76" s="25"/>
+      <c r="Y76" s="25"/>
+      <c r="Z76" s="25"/>
+      <c r="AA76" s="25"/>
+      <c r="AB76" s="25"/>
+      <c r="AC76" s="25"/>
+      <c r="AD76" s="25"/>
+      <c r="AE76" s="25"/>
+      <c r="AF76" s="25"/>
+      <c r="AG76" s="25"/>
+      <c r="AH76" s="25"/>
+      <c r="AI76" s="26"/>
       <c r="AO76" s="7"/>
       <c r="BB76" s="7"/>
     </row>
     <row r="77" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A77" s="6"/>
       <c r="D77" s="7"/>
-      <c r="Q77" s="7"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="25"/>
+      <c r="J77" s="25"/>
+      <c r="K77" s="25"/>
+      <c r="L77" s="25"/>
+      <c r="M77" s="25"/>
+      <c r="N77" s="25"/>
+      <c r="O77" s="25"/>
+      <c r="P77" s="25"/>
+      <c r="Q77" s="26"/>
       <c r="S77" s="6"/>
       <c r="V77" s="7"/>
-      <c r="AI77" s="7"/>
+      <c r="W77" s="25"/>
+      <c r="X77" s="25"/>
+      <c r="Y77" s="25"/>
+      <c r="Z77" s="25"/>
+      <c r="AA77" s="25"/>
+      <c r="AB77" s="25"/>
+      <c r="AC77" s="25"/>
+      <c r="AD77" s="25"/>
+      <c r="AE77" s="25"/>
+      <c r="AF77" s="25"/>
+      <c r="AG77" s="25"/>
+      <c r="AH77" s="25"/>
+      <c r="AI77" s="26"/>
       <c r="AL77" s="6"/>
       <c r="AO77" s="7"/>
       <c r="BB77" s="7"/>
     </row>
     <row r="78" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D78" s="7"/>
-      <c r="Q78" s="7"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="25"/>
+      <c r="L78" s="25"/>
+      <c r="M78" s="25"/>
+      <c r="N78" s="25"/>
+      <c r="O78" s="25"/>
+      <c r="P78" s="25"/>
+      <c r="Q78" s="26"/>
       <c r="V78" s="7"/>
-      <c r="AI78" s="7"/>
+      <c r="W78" s="25"/>
+      <c r="X78" s="25"/>
+      <c r="Y78" s="25"/>
+      <c r="Z78" s="25"/>
+      <c r="AA78" s="25"/>
+      <c r="AB78" s="25"/>
+      <c r="AC78" s="25"/>
+      <c r="AD78" s="25"/>
+      <c r="AE78" s="25"/>
+      <c r="AF78" s="25"/>
+      <c r="AG78" s="25"/>
+      <c r="AH78" s="25"/>
+      <c r="AI78" s="26"/>
       <c r="AO78" s="7"/>
       <c r="BB78" s="7"/>
     </row>
@@ -14400,12 +16291,36 @@
         <v>13</v>
       </c>
       <c r="D79" s="7"/>
-      <c r="Q79" s="7"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="25"/>
+      <c r="I79" s="25"/>
+      <c r="J79" s="25"/>
+      <c r="K79" s="25"/>
+      <c r="L79" s="25"/>
+      <c r="M79" s="25"/>
+      <c r="N79" s="25"/>
+      <c r="O79" s="25"/>
+      <c r="P79" s="25"/>
+      <c r="Q79" s="26"/>
       <c r="S79" s="12" t="s">
         <v>13</v>
       </c>
       <c r="V79" s="7"/>
-      <c r="AI79" s="7"/>
+      <c r="W79" s="25"/>
+      <c r="X79" s="25"/>
+      <c r="Y79" s="25"/>
+      <c r="Z79" s="25"/>
+      <c r="AA79" s="25"/>
+      <c r="AB79" s="25"/>
+      <c r="AC79" s="25"/>
+      <c r="AD79" s="25"/>
+      <c r="AE79" s="25"/>
+      <c r="AF79" s="25"/>
+      <c r="AG79" s="25"/>
+      <c r="AH79" s="25"/>
+      <c r="AI79" s="26"/>
       <c r="AL79" s="12" t="s">
         <v>13</v>
       </c>
@@ -14415,10 +16330,34 @@
     <row r="80" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A80" s="6"/>
       <c r="D80" s="7"/>
-      <c r="Q80" s="7"/>
+      <c r="E80" s="25"/>
+      <c r="F80" s="25"/>
+      <c r="G80" s="25"/>
+      <c r="H80" s="25"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="25"/>
+      <c r="L80" s="25"/>
+      <c r="M80" s="25"/>
+      <c r="N80" s="25"/>
+      <c r="O80" s="25"/>
+      <c r="P80" s="25"/>
+      <c r="Q80" s="26"/>
       <c r="S80" s="6"/>
       <c r="V80" s="7"/>
-      <c r="AI80" s="7"/>
+      <c r="W80" s="25"/>
+      <c r="X80" s="25"/>
+      <c r="Y80" s="25"/>
+      <c r="Z80" s="25"/>
+      <c r="AA80" s="25"/>
+      <c r="AB80" s="25"/>
+      <c r="AC80" s="25"/>
+      <c r="AD80" s="25"/>
+      <c r="AE80" s="25"/>
+      <c r="AF80" s="25"/>
+      <c r="AG80" s="25"/>
+      <c r="AH80" s="25"/>
+      <c r="AI80" s="26"/>
       <c r="AL80" s="6"/>
       <c r="AO80" s="7"/>
       <c r="BB80" s="7"/>
@@ -14426,10 +16365,34 @@
     <row r="81" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A81" s="6"/>
       <c r="D81" s="7"/>
-      <c r="Q81" s="7"/>
+      <c r="E81" s="25"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
+      <c r="H81" s="25"/>
+      <c r="I81" s="25"/>
+      <c r="J81" s="25"/>
+      <c r="K81" s="25"/>
+      <c r="L81" s="25"/>
+      <c r="M81" s="25"/>
+      <c r="N81" s="25"/>
+      <c r="O81" s="25"/>
+      <c r="P81" s="25"/>
+      <c r="Q81" s="26"/>
       <c r="S81" s="6"/>
       <c r="V81" s="7"/>
-      <c r="AI81" s="7"/>
+      <c r="W81" s="25"/>
+      <c r="X81" s="25"/>
+      <c r="Y81" s="25"/>
+      <c r="Z81" s="25"/>
+      <c r="AA81" s="25"/>
+      <c r="AB81" s="25"/>
+      <c r="AC81" s="25"/>
+      <c r="AD81" s="25"/>
+      <c r="AE81" s="25"/>
+      <c r="AF81" s="25"/>
+      <c r="AG81" s="25"/>
+      <c r="AH81" s="25"/>
+      <c r="AI81" s="26"/>
       <c r="AL81" s="6"/>
       <c r="AO81" s="7"/>
       <c r="BB81" s="7"/>
@@ -14437,31 +16400,101 @@
     <row r="82" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A82" s="6"/>
       <c r="D82" s="7"/>
-      <c r="Q82" s="7"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
+      <c r="H82" s="25"/>
+      <c r="I82" s="25"/>
+      <c r="J82" s="25"/>
+      <c r="K82" s="25"/>
+      <c r="L82" s="25"/>
+      <c r="M82" s="25"/>
+      <c r="N82" s="25"/>
+      <c r="O82" s="25"/>
+      <c r="P82" s="25"/>
+      <c r="Q82" s="26"/>
       <c r="S82" s="6"/>
       <c r="V82" s="7"/>
-      <c r="AI82" s="7"/>
+      <c r="W82" s="25"/>
+      <c r="X82" s="25"/>
+      <c r="Y82" s="25"/>
+      <c r="Z82" s="25"/>
+      <c r="AA82" s="25"/>
+      <c r="AB82" s="25"/>
+      <c r="AC82" s="25"/>
+      <c r="AD82" s="25"/>
+      <c r="AE82" s="25"/>
+      <c r="AF82" s="25"/>
+      <c r="AG82" s="25"/>
+      <c r="AH82" s="25"/>
+      <c r="AI82" s="26"/>
       <c r="AL82" s="6"/>
       <c r="AO82" s="7"/>
       <c r="BB82" s="7"/>
     </row>
     <row r="83" spans="1:54" x14ac:dyDescent="0.4">
       <c r="D83" s="7"/>
-      <c r="Q83" s="7"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="25"/>
+      <c r="G83" s="25"/>
+      <c r="H83" s="25"/>
+      <c r="I83" s="25"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="25"/>
+      <c r="L83" s="25"/>
+      <c r="M83" s="25"/>
+      <c r="N83" s="25"/>
+      <c r="O83" s="25"/>
+      <c r="P83" s="25"/>
+      <c r="Q83" s="26"/>
       <c r="V83" s="7"/>
-      <c r="AI83" s="7"/>
+      <c r="W83" s="25"/>
+      <c r="X83" s="25"/>
+      <c r="Y83" s="25"/>
+      <c r="Z83" s="25"/>
+      <c r="AA83" s="25"/>
+      <c r="AB83" s="25"/>
+      <c r="AC83" s="25"/>
+      <c r="AD83" s="25"/>
+      <c r="AE83" s="25"/>
+      <c r="AF83" s="25"/>
+      <c r="AG83" s="25"/>
+      <c r="AH83" s="25"/>
+      <c r="AI83" s="26"/>
       <c r="AO83" s="7"/>
       <c r="BB83" s="7"/>
     </row>
     <row r="84" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A84" s="6"/>
       <c r="D84" s="7"/>
-      <c r="I84" s="11"/>
-      <c r="Q84" s="7"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="30"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="25"/>
+      <c r="L84" s="25"/>
+      <c r="M84" s="25"/>
+      <c r="N84" s="25"/>
+      <c r="O84" s="25"/>
+      <c r="P84" s="25"/>
+      <c r="Q84" s="26"/>
       <c r="S84" s="6"/>
       <c r="V84" s="7"/>
-      <c r="AA84" s="11"/>
-      <c r="AI84" s="7"/>
+      <c r="W84" s="25"/>
+      <c r="X84" s="25"/>
+      <c r="Y84" s="25"/>
+      <c r="Z84" s="25"/>
+      <c r="AA84" s="30"/>
+      <c r="AB84" s="25"/>
+      <c r="AC84" s="25"/>
+      <c r="AD84" s="25"/>
+      <c r="AE84" s="25"/>
+      <c r="AF84" s="25"/>
+      <c r="AG84" s="25"/>
+      <c r="AH84" s="25"/>
+      <c r="AI84" s="26"/>
       <c r="AL84" s="6"/>
       <c r="AO84" s="7"/>
       <c r="AT84" s="11"/>
@@ -14470,10 +16503,34 @@
     <row r="85" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A85" s="6"/>
       <c r="D85" s="7"/>
-      <c r="Q85" s="7"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="25"/>
+      <c r="G85" s="25"/>
+      <c r="H85" s="25"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="25"/>
+      <c r="L85" s="25"/>
+      <c r="M85" s="25"/>
+      <c r="N85" s="25"/>
+      <c r="O85" s="25"/>
+      <c r="P85" s="25"/>
+      <c r="Q85" s="26"/>
       <c r="S85" s="6"/>
       <c r="V85" s="7"/>
-      <c r="AI85" s="7"/>
+      <c r="W85" s="25"/>
+      <c r="X85" s="25"/>
+      <c r="Y85" s="25"/>
+      <c r="Z85" s="25"/>
+      <c r="AA85" s="25"/>
+      <c r="AB85" s="25"/>
+      <c r="AC85" s="25"/>
+      <c r="AD85" s="25"/>
+      <c r="AE85" s="25"/>
+      <c r="AF85" s="25"/>
+      <c r="AG85" s="25"/>
+      <c r="AH85" s="25"/>
+      <c r="AI85" s="26"/>
       <c r="AL85" s="6"/>
       <c r="AO85" s="7"/>
       <c r="BB85" s="7"/>
@@ -14481,10 +16538,34 @@
     <row r="86" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A86" s="6"/>
       <c r="D86" s="7"/>
-      <c r="Q86" s="7"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="25"/>
+      <c r="H86" s="25"/>
+      <c r="I86" s="25"/>
+      <c r="J86" s="25"/>
+      <c r="K86" s="25"/>
+      <c r="L86" s="25"/>
+      <c r="M86" s="25"/>
+      <c r="N86" s="25"/>
+      <c r="O86" s="25"/>
+      <c r="P86" s="25"/>
+      <c r="Q86" s="26"/>
       <c r="S86" s="6"/>
       <c r="V86" s="7"/>
-      <c r="AI86" s="7"/>
+      <c r="W86" s="25"/>
+      <c r="X86" s="25"/>
+      <c r="Y86" s="25"/>
+      <c r="Z86" s="25"/>
+      <c r="AA86" s="25"/>
+      <c r="AB86" s="25"/>
+      <c r="AC86" s="25"/>
+      <c r="AD86" s="25"/>
+      <c r="AE86" s="25"/>
+      <c r="AF86" s="25"/>
+      <c r="AG86" s="25"/>
+      <c r="AH86" s="25"/>
+      <c r="AI86" s="26"/>
       <c r="AL86" s="6"/>
       <c r="AO86" s="7"/>
       <c r="BB86" s="7"/>
@@ -14492,10 +16573,34 @@
     <row r="87" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A87" s="6"/>
       <c r="D87" s="7"/>
-      <c r="Q87" s="7"/>
+      <c r="E87" s="25"/>
+      <c r="F87" s="25"/>
+      <c r="G87" s="25"/>
+      <c r="H87" s="25"/>
+      <c r="I87" s="25"/>
+      <c r="J87" s="25"/>
+      <c r="K87" s="25"/>
+      <c r="L87" s="25"/>
+      <c r="M87" s="25"/>
+      <c r="N87" s="25"/>
+      <c r="O87" s="25"/>
+      <c r="P87" s="25"/>
+      <c r="Q87" s="26"/>
       <c r="S87" s="6"/>
       <c r="V87" s="7"/>
-      <c r="AI87" s="7"/>
+      <c r="W87" s="25"/>
+      <c r="X87" s="25"/>
+      <c r="Y87" s="25"/>
+      <c r="Z87" s="25"/>
+      <c r="AA87" s="25"/>
+      <c r="AB87" s="25"/>
+      <c r="AC87" s="25"/>
+      <c r="AD87" s="25"/>
+      <c r="AE87" s="25"/>
+      <c r="AF87" s="25"/>
+      <c r="AG87" s="25"/>
+      <c r="AH87" s="25"/>
+      <c r="AI87" s="26"/>
       <c r="AL87" s="6"/>
       <c r="AO87" s="7"/>
       <c r="BB87" s="7"/>
@@ -14503,10 +16608,34 @@
     <row r="88" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A88" s="6"/>
       <c r="D88" s="7"/>
-      <c r="Q88" s="7"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="25"/>
+      <c r="J88" s="25"/>
+      <c r="K88" s="25"/>
+      <c r="L88" s="25"/>
+      <c r="M88" s="25"/>
+      <c r="N88" s="25"/>
+      <c r="O88" s="25"/>
+      <c r="P88" s="25"/>
+      <c r="Q88" s="26"/>
       <c r="S88" s="6"/>
       <c r="V88" s="7"/>
-      <c r="AI88" s="7"/>
+      <c r="W88" s="25"/>
+      <c r="X88" s="25"/>
+      <c r="Y88" s="25"/>
+      <c r="Z88" s="25"/>
+      <c r="AA88" s="25"/>
+      <c r="AB88" s="25"/>
+      <c r="AC88" s="25"/>
+      <c r="AD88" s="25"/>
+      <c r="AE88" s="25"/>
+      <c r="AF88" s="25"/>
+      <c r="AG88" s="25"/>
+      <c r="AH88" s="25"/>
+      <c r="AI88" s="26"/>
       <c r="AL88" s="6"/>
       <c r="AO88" s="7"/>
       <c r="BB88" s="7"/>
@@ -14514,10 +16643,34 @@
     <row r="89" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A89" s="6"/>
       <c r="D89" s="7"/>
-      <c r="Q89" s="7"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
+      <c r="H89" s="25"/>
+      <c r="I89" s="25"/>
+      <c r="J89" s="25"/>
+      <c r="K89" s="25"/>
+      <c r="L89" s="25"/>
+      <c r="M89" s="25"/>
+      <c r="N89" s="25"/>
+      <c r="O89" s="25"/>
+      <c r="P89" s="25"/>
+      <c r="Q89" s="26"/>
       <c r="S89" s="6"/>
       <c r="V89" s="7"/>
-      <c r="AI89" s="7"/>
+      <c r="W89" s="25"/>
+      <c r="X89" s="25"/>
+      <c r="Y89" s="25"/>
+      <c r="Z89" s="25"/>
+      <c r="AA89" s="25"/>
+      <c r="AB89" s="25"/>
+      <c r="AC89" s="25"/>
+      <c r="AD89" s="25"/>
+      <c r="AE89" s="25"/>
+      <c r="AF89" s="25"/>
+      <c r="AG89" s="25"/>
+      <c r="AH89" s="25"/>
+      <c r="AI89" s="26"/>
       <c r="AL89" s="6"/>
       <c r="AO89" s="7"/>
       <c r="BB89" s="7"/>
@@ -14525,10 +16678,34 @@
     <row r="90" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A90" s="6"/>
       <c r="D90" s="7"/>
-      <c r="Q90" s="7"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
+      <c r="H90" s="25"/>
+      <c r="I90" s="25"/>
+      <c r="J90" s="25"/>
+      <c r="K90" s="25"/>
+      <c r="L90" s="25"/>
+      <c r="M90" s="25"/>
+      <c r="N90" s="25"/>
+      <c r="O90" s="25"/>
+      <c r="P90" s="25"/>
+      <c r="Q90" s="26"/>
       <c r="S90" s="6"/>
       <c r="V90" s="7"/>
-      <c r="AI90" s="7"/>
+      <c r="W90" s="25"/>
+      <c r="X90" s="25"/>
+      <c r="Y90" s="25"/>
+      <c r="Z90" s="25"/>
+      <c r="AA90" s="25"/>
+      <c r="AB90" s="25"/>
+      <c r="AC90" s="25"/>
+      <c r="AD90" s="25"/>
+      <c r="AE90" s="25"/>
+      <c r="AF90" s="25"/>
+      <c r="AG90" s="25"/>
+      <c r="AH90" s="25"/>
+      <c r="AI90" s="26"/>
       <c r="AL90" s="6"/>
       <c r="AO90" s="7"/>
       <c r="BB90" s="7"/>
@@ -14536,10 +16713,34 @@
     <row r="91" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A91" s="6"/>
       <c r="D91" s="7"/>
-      <c r="Q91" s="7"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
+      <c r="H91" s="25"/>
+      <c r="I91" s="25"/>
+      <c r="J91" s="25"/>
+      <c r="K91" s="25"/>
+      <c r="L91" s="25"/>
+      <c r="M91" s="25"/>
+      <c r="N91" s="25"/>
+      <c r="O91" s="25"/>
+      <c r="P91" s="25"/>
+      <c r="Q91" s="26"/>
       <c r="S91" s="6"/>
       <c r="V91" s="7"/>
-      <c r="AI91" s="7"/>
+      <c r="W91" s="25"/>
+      <c r="X91" s="25"/>
+      <c r="Y91" s="25"/>
+      <c r="Z91" s="25"/>
+      <c r="AA91" s="25"/>
+      <c r="AB91" s="25"/>
+      <c r="AC91" s="25"/>
+      <c r="AD91" s="25"/>
+      <c r="AE91" s="25"/>
+      <c r="AF91" s="25"/>
+      <c r="AG91" s="25"/>
+      <c r="AH91" s="25"/>
+      <c r="AI91" s="26"/>
       <c r="AL91" s="6"/>
       <c r="AO91" s="7"/>
       <c r="BB91" s="7"/>
@@ -14549,36 +16750,36 @@
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
       <c r="D92" s="10"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="9"/>
-      <c r="J92" s="9"/>
-      <c r="K92" s="9"/>
-      <c r="L92" s="9"/>
-      <c r="M92" s="9"/>
-      <c r="N92" s="9"/>
-      <c r="O92" s="9"/>
-      <c r="P92" s="9"/>
-      <c r="Q92" s="10"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="28"/>
+      <c r="J92" s="28"/>
+      <c r="K92" s="28"/>
+      <c r="L92" s="28"/>
+      <c r="M92" s="28"/>
+      <c r="N92" s="28"/>
+      <c r="O92" s="28"/>
+      <c r="P92" s="28"/>
+      <c r="Q92" s="29"/>
       <c r="S92" s="8"/>
       <c r="T92" s="9"/>
       <c r="U92" s="9"/>
       <c r="V92" s="10"/>
-      <c r="W92" s="9"/>
-      <c r="X92" s="9"/>
-      <c r="Y92" s="9"/>
-      <c r="Z92" s="9"/>
-      <c r="AA92" s="9"/>
-      <c r="AB92" s="9"/>
-      <c r="AC92" s="9"/>
-      <c r="AD92" s="9"/>
-      <c r="AE92" s="9"/>
-      <c r="AF92" s="9"/>
-      <c r="AG92" s="9"/>
-      <c r="AH92" s="9"/>
-      <c r="AI92" s="10"/>
+      <c r="W92" s="28"/>
+      <c r="X92" s="28"/>
+      <c r="Y92" s="28"/>
+      <c r="Z92" s="28"/>
+      <c r="AA92" s="28"/>
+      <c r="AB92" s="28"/>
+      <c r="AC92" s="28"/>
+      <c r="AD92" s="28"/>
+      <c r="AE92" s="28"/>
+      <c r="AF92" s="28"/>
+      <c r="AG92" s="28"/>
+      <c r="AH92" s="28"/>
+      <c r="AI92" s="29"/>
       <c r="AL92" s="8"/>
       <c r="AM92" s="9"/>
       <c r="AN92" s="9"/>
